--- a/Thesis/data/Feature_selection.xlsx
+++ b/Thesis/data/Feature_selection.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hugonogueira/Desktop/Thesis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hugonogueira/git_hugo/feup/Thesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C700C8E4-6D0A-1042-9C83-1258BF6B716E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E734F5F5-917D-E84D-BA3B-39CA335B0352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Indicators" sheetId="3" r:id="rId1"/>
-    <sheet name="crop_calendear" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="Indicators (2)" sheetId="6" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="3" r:id="rId2"/>
+    <sheet name="crop_calendear" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Indicators!$A$1:$AT$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Indicators!$B$1:$AU$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Indicators (2)'!$B$1:$AU$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,12 +44,13 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={F9B77A34-3A35-684D-8686-B845558400A6}</author>
-    <author>tc={4AE4F941-CF5F-9349-B2A9-C41DF6C89ABE}</author>
-    <author>tc={2273ADF4-1408-3445-B966-23F88A2C273C}</author>
+    <author>tc={85AE1B91-C126-5F40-A259-386B8EED939D}</author>
+    <author>tc={05AC948E-F868-9348-BDAB-D6CB890AED7C}</author>
+    <author>tc={5B91C0ED-1A70-1642-9DD5-98675520613E}</author>
+    <author>tc={B9C5178D-6ECE-F642-A270-F10E553765A8}</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{F9B77A34-3A35-684D-8686-B845558400A6}">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{85AE1B91-C126-5F40-A259-386B8EED939D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,7 +59,16 @@
 </t>
       </text>
     </comment>
-    <comment ref="A23" authorId="1" shapeId="0" xr:uid="{4AE4F941-CF5F-9349-B2A9-C41DF6C89ABE}">
+    <comment ref="Z14" authorId="1" shapeId="0" xr:uid="{05AC948E-F868-9348-BDAB-D6CB890AED7C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    aqui tinhamos inicialmente o valor de 10 que repetia o mesdmo valor do A1 e entao A1 = A2 não faz sentido. 
+Coloquei 20 em A2 para ter um periodo mais alatgado</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="2" shapeId="0" xr:uid="{5B91C0ED-1A70-1642-9DD5-98675520613E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -65,7 +76,54 @@
     Nao considerar esta por indicacao do prof Mario</t>
       </text>
     </comment>
-    <comment ref="A55" authorId="2" shapeId="0" xr:uid="{2273ADF4-1408-3445-B966-23F88A2C273C}">
+    <comment ref="B55" authorId="3" shapeId="0" xr:uid="{B9C5178D-6ECE-F642-A270-F10E553765A8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    nao considerar esta por indicacao do prof Mario</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={F9B77A34-3A35-684D-8686-B845558400A6}</author>
+    <author>tc={20292B73-B2C2-AA48-86F9-5669E294B6E5}</author>
+    <author>tc={4AE4F941-CF5F-9349-B2A9-C41DF6C89ABE}</author>
+    <author>tc={2273ADF4-1408-3445-B966-23F88A2C273C}</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{F9B77A34-3A35-684D-8686-B845558400A6}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    control Hugo
+</t>
+      </text>
+    </comment>
+    <comment ref="Z14" authorId="1" shapeId="0" xr:uid="{20292B73-B2C2-AA48-86F9-5669E294B6E5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    aqui tinhamos inicialmente o valor de 10 que repetia o mesdmo valor do A1 e entao A1 = A2 não faz sentido. 
+Coloquei 20 em A2 para ter um periodo mais alatgado</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="2" shapeId="0" xr:uid="{4AE4F941-CF5F-9349-B2A9-C41DF6C89ABE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Nao considerar esta por indicacao do prof Mario</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="3" shapeId="0" xr:uid="{2273ADF4-1408-3445-B966-23F88A2C273C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -78,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="122">
   <si>
     <t>C</t>
   </si>
@@ -438,6 +496,12 @@
   </si>
   <si>
     <t>§</t>
+  </si>
+  <si>
+    <t>Metric descrition</t>
+  </si>
+  <si>
+    <t>average temperature</t>
   </si>
 </sst>
 </file>
@@ -670,7 +734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -781,16 +845,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4619,59 +4708,82 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B4" dT="2023-05-18T21:26:35.85" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{F9B77A34-3A35-684D-8686-B845558400A6}">
+  <threadedComment ref="C4" dT="2023-05-18T21:26:35.85" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{85AE1B91-C126-5F40-A259-386B8EED939D}">
     <text xml:space="preserve">control Hugo
 </text>
   </threadedComment>
-  <threadedComment ref="A23" dT="2023-05-30T11:22:30.51" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{4AE4F941-CF5F-9349-B2A9-C41DF6C89ABE}">
+  <threadedComment ref="Z14" dT="2023-08-05T16:43:05.63" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{05AC948E-F868-9348-BDAB-D6CB890AED7C}">
+    <text>aqui tinhamos inicialmente o valor de 10 que repetia o mesdmo valor do A1 e entao A1 = A2 não faz sentido. 
+Coloquei 20 em A2 para ter um periodo mais alatgado</text>
+  </threadedComment>
+  <threadedComment ref="B23" dT="2023-05-30T11:22:30.51" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{5B91C0ED-1A70-1642-9DD5-98675520613E}">
     <text>Nao considerar esta por indicacao do prof Mario</text>
   </threadedComment>
-  <threadedComment ref="A55" dT="2023-05-30T11:23:37.10" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{2273ADF4-1408-3445-B966-23F88A2C273C}">
+  <threadedComment ref="B55" dT="2023-05-30T11:23:37.10" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{B9C5178D-6ECE-F642-A270-F10E553765A8}">
+    <text>nao considerar esta por indicacao do prof Mario</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C4" dT="2023-05-18T21:26:35.85" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{F9B77A34-3A35-684D-8686-B845558400A6}">
+    <text xml:space="preserve">control Hugo
+</text>
+  </threadedComment>
+  <threadedComment ref="Z14" dT="2023-08-05T16:43:05.63" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{20292B73-B2C2-AA48-86F9-5669E294B6E5}">
+    <text>aqui tinhamos inicialmente o valor de 10 que repetia o mesdmo valor do A1 e entao A1 = A2 não faz sentido. 
+Coloquei 20 em A2 para ter um periodo mais alatgado</text>
+  </threadedComment>
+  <threadedComment ref="B23" dT="2023-05-30T11:22:30.51" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{4AE4F941-CF5F-9349-B2A9-C41DF6C89ABE}">
+    <text>Nao considerar esta por indicacao do prof Mario</text>
+  </threadedComment>
+  <threadedComment ref="B55" dT="2023-05-30T11:23:37.10" personId="{19C9D175-DBA7-F84E-B64B-0B28F7054C80}" id="{2273ADF4-1408-3445-B966-23F88A2C273C}">
     <text>nao considerar esta por indicacao do prof Mario</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7408B6-7988-E14C-85FF-DE6C69D77BFB}">
+  <dimension ref="A1:AU60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="29.5" style="1" customWidth="1"/>
-    <col min="2" max="3" width="6.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.33203125" style="1" customWidth="1"/>
-    <col min="6" max="10" width="4.5" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="0.83203125" style="1" customWidth="1"/>
-    <col min="12" max="18" width="3.5" style="1" customWidth="1"/>
-    <col min="19" max="19" width="0.6640625" style="1" customWidth="1"/>
-    <col min="20" max="26" width="3.5" style="1" customWidth="1"/>
-    <col min="27" max="27" width="0.6640625" style="1" customWidth="1"/>
-    <col min="28" max="34" width="3.5" style="1" customWidth="1"/>
-    <col min="35" max="35" width="1.1640625" style="1" customWidth="1"/>
-    <col min="36" max="42" width="3.5" style="1" customWidth="1"/>
-    <col min="43" max="43" width="0.83203125" style="1" customWidth="1"/>
-    <col min="44" max="46" width="4.5" style="1" customWidth="1"/>
-    <col min="47" max="16384" width="9.1640625" style="1"/>
+    <col min="1" max="1" width="9.1640625" style="1"/>
+    <col min="2" max="2" width="29.5" style="1" customWidth="1"/>
+    <col min="3" max="4" width="6.5" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" style="1" customWidth="1"/>
+    <col min="7" max="11" width="4.5" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="0.83203125" style="1" customWidth="1"/>
+    <col min="13" max="19" width="3.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="0.6640625" style="1" customWidth="1"/>
+    <col min="21" max="27" width="3.5" style="1" customWidth="1"/>
+    <col min="28" max="28" width="0.6640625" style="1" customWidth="1"/>
+    <col min="29" max="35" width="3.5" style="1" customWidth="1"/>
+    <col min="36" max="36" width="1.1640625" style="1" customWidth="1"/>
+    <col min="37" max="43" width="3.5" style="1" customWidth="1"/>
+    <col min="44" max="44" width="0.83203125" style="1" customWidth="1"/>
+    <col min="45" max="47" width="4.5" style="1" customWidth="1"/>
+    <col min="48" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="G1" s="1" t="s">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="H1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="9"/>
-      <c r="B2" s="3"/>
+    <row r="2" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="9"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="54"/>
       <c r="J2" s="54"/>
       <c r="K2" s="54"/>
       <c r="L2" s="54"/>
@@ -4705,188 +4817,191 @@
       <c r="AN2" s="54"/>
       <c r="AO2" s="54"/>
       <c r="AP2" s="54"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="3"/>
+      <c r="AQ2" s="54"/>
+      <c r="AR2" s="4"/>
       <c r="AS2" s="3"/>
-      <c r="AT2" s="10"/>
-    </row>
-    <row r="3" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="11" t="s">
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="10"/>
+    </row>
+    <row r="3" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="53" t="s">
+      <c r="F3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="M3" s="53"/>
       <c r="N3" s="53"/>
       <c r="O3" s="53"/>
       <c r="P3" s="53"/>
       <c r="Q3" s="53"/>
       <c r="R3" s="53"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="53" t="s">
+      <c r="S3" s="53"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="U3" s="53"/>
       <c r="V3" s="53"/>
       <c r="W3" s="53"/>
       <c r="X3" s="53"/>
       <c r="Y3" s="53"/>
       <c r="Z3" s="53"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="53" t="s">
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="AC3" s="53"/>
       <c r="AD3" s="53"/>
       <c r="AE3" s="53"/>
       <c r="AF3" s="53"/>
       <c r="AG3" s="53"/>
       <c r="AH3" s="53"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="53" t="s">
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="AK3" s="53"/>
       <c r="AL3" s="53"/>
       <c r="AM3" s="53"/>
       <c r="AN3" s="53"/>
       <c r="AO3" s="53"/>
       <c r="AP3" s="53"/>
-      <c r="AQ3" s="12"/>
-      <c r="AR3" s="55" t="s">
+      <c r="AQ3" s="53"/>
+      <c r="AR3" s="12"/>
+      <c r="AS3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="AS3" s="55"/>
-      <c r="AT3" s="56"/>
-    </row>
-    <row r="4" spans="1:46" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="13" t="s">
+      <c r="AT3" s="55"/>
+      <c r="AU3" s="56"/>
+    </row>
+    <row r="4" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="C4" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="49"/>
+      <c r="E4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="H4" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="I4" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="45" t="s">
+      <c r="J4" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="45" t="s">
+      <c r="K4" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="7"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="2" t="s">
+      <c r="S4" s="2"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="26" t="s">
+      <c r="X4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2" t="s">
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AE4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AE4" s="26" t="s">
+      <c r="AF4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AF4" s="2" t="s">
+      <c r="AG4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="2" t="s">
+      <c r="AH4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2" t="s">
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AL4" s="2" t="s">
+      <c r="AM4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AM4" s="26" t="s">
+      <c r="AN4" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AN4" s="2" t="s">
+      <c r="AO4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AO4" s="2" t="s">
+      <c r="AP4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="5"/>
-      <c r="AR4" s="6">
-        <v>1</v>
-      </c>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="5"/>
       <c r="AS4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="6">
         <v>2</v>
       </c>
-      <c r="AT4" s="28" t="s">
+      <c r="AU4" s="28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A5" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="48"/>
+    <row r="5" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="C5" s="48"/>
-      <c r="D5" s="12"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="42"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
@@ -4924,34 +5039,37 @@
       <c r="AQ5" s="12"/>
       <c r="AR5" s="12"/>
       <c r="AS5" s="12"/>
-      <c r="AT5" s="15"/>
-    </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A6" s="11" t="s">
+      <c r="AT5" s="12"/>
+      <c r="AU5" s="15"/>
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="1">
-        <f t="shared" ref="B6:B25" si="0">IF(C6=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="8" t="s">
+      <c r="C6" s="1">
+        <f t="shared" ref="C6:C25" si="0">IF(D6=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="43"/>
-      <c r="H6" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="H6" s="43"/>
       <c r="I6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
@@ -4962,61 +5080,61 @@
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
-      <c r="V6" s="47">
+      <c r="V6" s="8"/>
+      <c r="W6" s="47">
         <v>10</v>
       </c>
-      <c r="W6" s="47">
+      <c r="X6" s="47">
         <v>15</v>
       </c>
-      <c r="X6" s="47">
+      <c r="Y6" s="47">
         <v>10</v>
       </c>
-      <c r="Y6" s="8"/>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8"/>
-      <c r="AE6" s="47">
-        <v>20</v>
-      </c>
+      <c r="AE6" s="8"/>
       <c r="AF6" s="47">
         <v>20</v>
       </c>
-      <c r="AG6" s="8"/>
+      <c r="AG6" s="47">
+        <v>20</v>
+      </c>
       <c r="AH6" s="8"/>
       <c r="AI6" s="8"/>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
-      <c r="AL6" s="47">
+      <c r="AL6" s="8"/>
+      <c r="AM6" s="47">
         <v>20</v>
       </c>
-      <c r="AM6" s="47">
+      <c r="AN6" s="47">
         <v>10</v>
       </c>
-      <c r="AN6" s="8"/>
       <c r="AO6" s="8"/>
       <c r="AP6" s="8"/>
-      <c r="AR6" s="1" t="s">
+      <c r="AQ6" s="8"/>
+      <c r="AS6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AS6" s="1" t="s">
+      <c r="AT6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AT6" s="17"/>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A7" s="11" t="s">
+      <c r="AU6" s="17"/>
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -5053,27 +5171,27 @@
       <c r="AN7" s="8"/>
       <c r="AO7" s="8"/>
       <c r="AP7" s="8"/>
-      <c r="AT7" s="17"/>
-    </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A8" s="11" t="s">
+      <c r="AQ7" s="8"/>
+      <c r="AU7" s="17"/>
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -5085,16 +5203,16 @@
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
-      <c r="V8" s="47">
-        <v>15</v>
-      </c>
+      <c r="V8" s="8"/>
       <c r="W8" s="47">
         <v>15</v>
       </c>
       <c r="X8" s="47">
         <v>15</v>
       </c>
-      <c r="Y8" s="8"/>
+      <c r="Y8" s="47">
+        <v>15</v>
+      </c>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
@@ -5112,21 +5230,21 @@
       <c r="AN8" s="8"/>
       <c r="AO8" s="8"/>
       <c r="AP8" s="8"/>
-      <c r="AT8" s="17"/>
-    </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A9" s="14" t="s">
+      <c r="AQ8" s="8"/>
+      <c r="AU8" s="17"/>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D9" s="12"/>
       <c r="E9" s="12"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="16"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="43"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
@@ -5165,24 +5283,24 @@
       <c r="AR9" s="16"/>
       <c r="AS9" s="16"/>
       <c r="AT9" s="16"/>
-    </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A10" s="11" t="s">
+      <c r="AU9" s="16"/>
+    </row>
+    <row r="10" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="43"/>
-      <c r="H10" s="8"/>
+      <c r="H10" s="43"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -5217,48 +5335,48 @@
       <c r="AN10" s="8"/>
       <c r="AO10" s="8"/>
       <c r="AP10" s="8"/>
-      <c r="AT10" s="17"/>
-    </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A11" s="11" t="s">
+      <c r="AQ10" s="8"/>
+      <c r="AU10" s="17"/>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1">
+      <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="8" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="8"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="47">
+      <c r="O11" s="8"/>
+      <c r="P11" s="47">
         <v>20</v>
       </c>
-      <c r="P11" s="47">
+      <c r="Q11" s="47">
         <v>30</v>
       </c>
-      <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
-      <c r="X11" s="47">
+      <c r="X11" s="8"/>
+      <c r="Y11" s="47">
         <v>10</v>
       </c>
-      <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
@@ -5276,21 +5394,21 @@
       <c r="AN11" s="8"/>
       <c r="AO11" s="8"/>
       <c r="AP11" s="8"/>
-      <c r="AT11" s="17"/>
-    </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A12" s="14" t="s">
+      <c r="AQ11" s="8"/>
+      <c r="AU11" s="17"/>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="1">
+      <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D12" s="12"/>
       <c r="E12" s="12"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="16"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
       <c r="K12" s="16"/>
@@ -5329,25 +5447,25 @@
       <c r="AR12" s="16"/>
       <c r="AS12" s="16"/>
       <c r="AT12" s="16"/>
-    </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A13" s="11" t="s">
+      <c r="AU12" s="16"/>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B13" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1">
+      <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="8" t="s">
+      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -5379,30 +5497,30 @@
       <c r="AN13" s="8"/>
       <c r="AO13" s="8"/>
       <c r="AP13" s="8"/>
-      <c r="AT13" s="17"/>
-    </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A14" s="11" t="s">
+      <c r="AQ13" s="8"/>
+      <c r="AU13" s="17"/>
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="8"/>
       <c r="J14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="8"/>
+      <c r="K14" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -5415,24 +5533,24 @@
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
-      <c r="X14" s="47">
-        <v>10</v>
-      </c>
+      <c r="X14" s="8"/>
       <c r="Y14" s="47">
         <v>10</v>
       </c>
-      <c r="Z14" s="8"/>
+      <c r="Z14" s="47">
+        <v>20</v>
+      </c>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
       <c r="AC14" s="8"/>
-      <c r="AD14" s="47">
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="47">
         <v>20</v>
       </c>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="47">
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="47">
         <v>20</v>
       </c>
-      <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8"/>
       <c r="AJ14" s="8"/>
@@ -5442,21 +5560,21 @@
       <c r="AN14" s="8"/>
       <c r="AO14" s="8"/>
       <c r="AP14" s="8"/>
-      <c r="AT14" s="17"/>
-    </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A15" s="14" t="s">
+      <c r="AQ14" s="8"/>
+      <c r="AU14" s="17"/>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="1">
+      <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="16"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="43"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -5495,33 +5613,33 @@
       <c r="AR15" s="16"/>
       <c r="AS15" s="16"/>
       <c r="AT15" s="16"/>
-    </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A16" s="11" t="s">
+      <c r="AU15" s="16"/>
+    </row>
+    <row r="16" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="1">
+      <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="12"/>
+      <c r="G16" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="43"/>
-      <c r="H16" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="H16" s="43"/>
       <c r="I16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K16" s="8"/>
+      <c r="K16" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -5534,10 +5652,10 @@
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
-      <c r="X16" s="47">
+      <c r="X16" s="8"/>
+      <c r="Y16" s="47">
         <v>10</v>
       </c>
-      <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
@@ -5550,41 +5668,41 @@
       <c r="AI16" s="8"/>
       <c r="AJ16" s="8"/>
       <c r="AK16" s="8"/>
-      <c r="AL16" s="47">
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="47">
         <v>10</v>
       </c>
-      <c r="AM16" s="8"/>
-      <c r="AN16" s="47">
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="47">
         <v>10</v>
       </c>
-      <c r="AO16" s="8"/>
       <c r="AP16" s="8"/>
-      <c r="AT16" s="17"/>
-    </row>
-    <row r="17" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A17" s="11" t="s">
+      <c r="AQ16" s="8"/>
+      <c r="AU16" s="17"/>
+    </row>
+    <row r="17" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B17" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="1">
+      <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="43"/>
       <c r="I17" s="8" t="s">
         <v>4</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K17" s="8"/>
+      <c r="K17" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -5596,49 +5714,49 @@
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
-      <c r="W17" s="47">
+      <c r="W17" s="8"/>
+      <c r="X17" s="47">
         <v>15</v>
       </c>
-      <c r="X17" s="47">
+      <c r="Y17" s="47">
         <v>20</v>
       </c>
-      <c r="Y17" s="8"/>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8"/>
-      <c r="AD17" s="47">
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="47">
         <v>20</v>
       </c>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="47">
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="47">
         <v>20</v>
       </c>
-      <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
       <c r="AI17" s="8"/>
       <c r="AJ17" s="8"/>
       <c r="AK17" s="8"/>
       <c r="AL17" s="8"/>
-      <c r="AM17" s="47">
-        <v>10</v>
-      </c>
+      <c r="AM17" s="8"/>
       <c r="AN17" s="47">
         <v>10</v>
       </c>
-      <c r="AO17" s="8"/>
+      <c r="AO17" s="47">
+        <v>10</v>
+      </c>
       <c r="AP17" s="8"/>
-      <c r="AT17" s="17"/>
-    </row>
-    <row r="18" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A18" s="18" t="s">
+      <c r="AQ17" s="8"/>
+      <c r="AU17" s="17"/>
+    </row>
+    <row r="18" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B18" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
@@ -5676,59 +5794,59 @@
       <c r="AO18" s="8"/>
       <c r="AP18" s="8"/>
       <c r="AQ18" s="8"/>
-      <c r="AR18" s="33"/>
-      <c r="AS18" s="8"/>
+      <c r="AR18" s="8"/>
+      <c r="AS18" s="33"/>
       <c r="AT18" s="8"/>
-    </row>
-    <row r="19" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A19" s="11" t="s">
+      <c r="AU18" s="8"/>
+    </row>
+    <row r="19" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B19" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="1">
+      <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="E19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="H19" s="8"/>
       <c r="I19" s="8" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K19" s="8"/>
+      <c r="K19" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
-      <c r="O19" s="47">
+      <c r="O19" s="8"/>
+      <c r="P19" s="47">
         <v>10</v>
       </c>
-      <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
-      <c r="T19" s="50">
+      <c r="T19" s="8"/>
+      <c r="U19" s="50">
         <v>30</v>
       </c>
-      <c r="U19" s="50">
+      <c r="V19" s="50">
         <v>20</v>
       </c>
-      <c r="V19" s="50">
+      <c r="W19" s="50">
         <v>10</v>
       </c>
-      <c r="W19" s="8"/>
-      <c r="X19" s="50">
+      <c r="X19" s="8"/>
+      <c r="Y19" s="50">
         <v>10</v>
       </c>
-      <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
@@ -5742,28 +5860,28 @@
       <c r="AJ19" s="8"/>
       <c r="AK19" s="8"/>
       <c r="AL19" s="8"/>
-      <c r="AM19" s="50">
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="50">
         <v>10</v>
       </c>
-      <c r="AN19" s="8"/>
       <c r="AO19" s="8"/>
       <c r="AP19" s="8"/>
-      <c r="AR19" s="8"/>
-      <c r="AT19" s="17"/>
-    </row>
-    <row r="20" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A20" s="14" t="s">
+      <c r="AQ19" s="8"/>
+      <c r="AS19" s="8"/>
+      <c r="AU19" s="17"/>
+    </row>
+    <row r="20" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B20" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D20" s="12"/>
       <c r="E20" s="12"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="16"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="43"/>
       <c r="I20" s="16"/>
       <c r="J20" s="16"/>
       <c r="K20" s="16"/>
@@ -5799,34 +5917,34 @@
       <c r="AO20" s="16"/>
       <c r="AP20" s="16"/>
       <c r="AQ20" s="16"/>
-      <c r="AR20" s="8"/>
-      <c r="AS20" s="16"/>
+      <c r="AR20" s="16"/>
+      <c r="AS20" s="8"/>
       <c r="AT20" s="16"/>
-    </row>
-    <row r="21" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A21" s="11" t="s">
+      <c r="AU20" s="16"/>
+    </row>
+    <row r="21" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B21" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="1">
+      <c r="C21" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="33" t="s">
+      <c r="E21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="43"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="8"/>
       <c r="J21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="8"/>
+      <c r="K21" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -5858,30 +5976,30 @@
       <c r="AN21" s="8"/>
       <c r="AO21" s="8"/>
       <c r="AP21" s="8"/>
-      <c r="AT21" s="17"/>
-    </row>
-    <row r="22" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A22" s="11" t="s">
+      <c r="AQ21" s="8"/>
+      <c r="AU21" s="17"/>
+    </row>
+    <row r="22" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="1">
+      <c r="C22" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="E22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="8"/>
       <c r="J22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="8"/>
+      <c r="K22" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -5894,13 +6012,13 @@
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
-      <c r="X22" s="52">
+      <c r="X22" s="8"/>
+      <c r="Y22" s="52">
         <v>15</v>
       </c>
-      <c r="Y22" s="52">
+      <c r="Z22" s="52">
         <v>20</v>
       </c>
-      <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
       <c r="AC22" s="8"/>
@@ -5912,35 +6030,35 @@
       <c r="AI22" s="8"/>
       <c r="AJ22" s="8"/>
       <c r="AK22" s="8"/>
-      <c r="AL22" s="52">
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="52">
         <v>20</v>
       </c>
-      <c r="AM22" s="8"/>
-      <c r="AN22" s="52">
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="52">
         <v>20</v>
       </c>
-      <c r="AO22" s="8"/>
       <c r="AP22" s="8"/>
-      <c r="AT22" s="17"/>
-    </row>
-    <row r="23" spans="1:46" s="32" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="34" t="s">
+      <c r="AQ22" s="8"/>
+      <c r="AU22" s="17"/>
+    </row>
+    <row r="23" spans="2:47" s="32" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="32">
+      <c r="C23" s="32">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F23" s="33"/>
       <c r="G23" s="33"/>
       <c r="H23" s="33"/>
-      <c r="I23" s="33" t="s">
-        <v>4</v>
-      </c>
+      <c r="I23" s="33"/>
       <c r="J23" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="K23" s="33"/>
+      <c r="K23" s="33" t="s">
+        <v>4</v>
+      </c>
       <c r="L23" s="33"/>
       <c r="M23" s="33"/>
       <c r="N23" s="33"/>
@@ -5953,58 +6071,58 @@
       <c r="U23" s="33"/>
       <c r="V23" s="33"/>
       <c r="W23" s="33"/>
-      <c r="Z23" s="51"/>
-      <c r="AA23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="AA23" s="51"/>
       <c r="AB23" s="33"/>
       <c r="AC23" s="33"/>
       <c r="AD23" s="33"/>
       <c r="AE23" s="33"/>
-      <c r="AF23" s="51">
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="51">
         <v>10</v>
       </c>
-      <c r="AG23" s="51">
+      <c r="AH23" s="51">
         <v>20</v>
       </c>
-      <c r="AH23" s="33"/>
       <c r="AI23" s="33"/>
       <c r="AJ23" s="33"/>
       <c r="AK23" s="33"/>
-      <c r="AL23" s="33">
+      <c r="AL23" s="33"/>
+      <c r="AM23" s="33">
         <v>20</v>
       </c>
-      <c r="AM23" s="33"/>
-      <c r="AN23" s="33">
+      <c r="AN23" s="33"/>
+      <c r="AO23" s="33">
         <v>20</v>
       </c>
-      <c r="AP23" s="33"/>
-      <c r="AT23" s="35"/>
-    </row>
-    <row r="24" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A24" s="11" t="s">
+      <c r="AQ23" s="33"/>
+      <c r="AU23" s="35"/>
+    </row>
+    <row r="24" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="1">
+      <c r="C24" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C24" s="1">
-        <f t="shared" ref="C23:C25" si="1">COUNTA(L24:AP24)</f>
+      <c r="D24" s="1">
+        <f t="shared" ref="D24:D25" si="1">COUNTA(M24:AQ24)</f>
         <v>6</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="8"/>
       <c r="J24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="8"/>
+      <c r="K24" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -6017,66 +6135,66 @@
       <c r="U24" s="8"/>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
-      <c r="X24" s="36">
+      <c r="X24" s="8"/>
+      <c r="Y24" s="36">
         <v>10</v>
       </c>
-      <c r="Y24" s="36">
+      <c r="Z24" s="36">
         <v>20</v>
       </c>
-      <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
       <c r="AC24" s="8"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
-      <c r="AF24" s="36">
+      <c r="AF24" s="8"/>
+      <c r="AG24" s="36">
         <v>10</v>
       </c>
-      <c r="AG24" s="36">
+      <c r="AH24" s="36">
         <v>20</v>
       </c>
-      <c r="AH24" s="8"/>
       <c r="AI24" s="8"/>
       <c r="AJ24" s="8"/>
       <c r="AK24" s="8"/>
-      <c r="AL24" s="8">
+      <c r="AL24" s="8"/>
+      <c r="AM24" s="8">
         <v>20</v>
       </c>
-      <c r="AM24" s="8"/>
-      <c r="AN24" s="8">
+      <c r="AN24" s="8"/>
+      <c r="AO24" s="8">
         <v>20</v>
       </c>
-      <c r="AP24" s="8"/>
-      <c r="AT24" s="17"/>
-    </row>
-    <row r="25" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A25" s="11" t="s">
+      <c r="AQ24" s="8"/>
+      <c r="AU24" s="17"/>
+    </row>
+    <row r="25" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B25" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="1">
+      <c r="C25" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C25" s="1">
+      <c r="D25" s="1">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="8" t="s">
+      <c r="F25" s="12"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K25" s="8"/>
+      <c r="K25" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
@@ -6089,13 +6207,13 @@
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
-      <c r="X25" s="36">
+      <c r="X25" s="8"/>
+      <c r="Y25" s="36">
         <v>10</v>
       </c>
-      <c r="Y25" s="36">
+      <c r="Z25" s="36">
         <v>20</v>
       </c>
-      <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
@@ -6110,18 +6228,18 @@
       <c r="AL25" s="8"/>
       <c r="AM25" s="8"/>
       <c r="AN25" s="8"/>
-      <c r="AP25" s="8"/>
-      <c r="AT25" s="17"/>
-    </row>
-    <row r="26" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A26" s="19"/>
-      <c r="B26" s="2"/>
+      <c r="AO25" s="8"/>
+      <c r="AQ25" s="8"/>
+      <c r="AU25" s="17"/>
+    </row>
+    <row r="26" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B26" s="19"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="6"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="41"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -6156,42 +6274,39 @@
       <c r="AN26" s="6"/>
       <c r="AO26" s="6"/>
       <c r="AP26" s="6"/>
-      <c r="AQ26" s="2"/>
+      <c r="AQ26" s="6"/>
       <c r="AR26" s="2"/>
       <c r="AS26" s="2"/>
-      <c r="AT26" s="20"/>
-    </row>
-    <row r="27" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A27" s="11" t="s">
+      <c r="AT26" s="2"/>
+      <c r="AU26" s="20"/>
+    </row>
+    <row r="27" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="1">
-        <f>COUNTA(F5:F26)</f>
+      <c r="F27" s="12"/>
+      <c r="G27" s="1">
+        <f>COUNTA(G5:G26)</f>
         <v>6</v>
       </c>
-      <c r="G27" s="42">
-        <f>COUNTA(G5:G26)</f>
+      <c r="H27" s="42">
+        <f>COUNTA(H5:H26)</f>
         <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <f>COUNTA(H5:H26)</f>
-        <v>6</v>
       </c>
       <c r="I27" s="1">
         <f>COUNTA(I5:I26)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J27" s="1">
         <f>COUNTA(J5:J26)</f>
+        <v>11</v>
+      </c>
+      <c r="K27" s="1">
+        <f>COUNTA(K5:K26)</f>
         <v>10</v>
       </c>
-      <c r="L27" s="1">
-        <f t="shared" ref="L27:R27" si="2">COUNTA(L5:L26)</f>
-        <v>0</v>
-      </c>
       <c r="M27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M27:S27" si="2">COUNTA(M5:M26)</f>
         <v>0</v>
       </c>
       <c r="N27" s="1">
@@ -6200,31 +6315,31 @@
       </c>
       <c r="O27" s="1">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T27" s="1">
-        <f t="shared" ref="T27:Z27" si="3">COUNTA(T5:T26)</f>
-        <v>1</v>
+      <c r="S27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="U27:AA27" si="3">COUNTA(U5:U26)</f>
         <v>1</v>
       </c>
       <c r="V27" s="1">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W27" s="1">
         <f t="shared" si="3"/>
@@ -6232,88 +6347,91 @@
       </c>
       <c r="X27" s="1">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y27" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z27" s="1">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AA27" s="1">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="1">
-        <f t="shared" ref="AB27:AH27" si="4">COUNTA(AB5:AB26)</f>
+      <c r="AC27" s="1">
+        <f t="shared" ref="AC27:AI27" si="4">COUNTA(AC5:AC26)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="1">
+      <c r="AD27" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="1">
+      <c r="AE27" s="1">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AE27" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="AF27" s="1">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="1">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH27" s="1">
         <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AI27" s="1">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ27" s="1">
-        <f t="shared" ref="AJ27:AP27" si="5">COUNTA(AJ5:AJ26)</f>
+      <c r="AK27" s="1">
+        <f t="shared" ref="AK27:AQ27" si="5">COUNTA(AK5:AK26)</f>
         <v>0</v>
       </c>
-      <c r="AK27" s="1">
+      <c r="AL27" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="1">
+      <c r="AM27" s="1">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="AM27" s="1">
+      <c r="AN27" s="1">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="AN27" s="1">
+      <c r="AO27" s="1">
         <f t="shared" si="5"/>
         <v>5</v>
-      </c>
-      <c r="AO27" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="AP27" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AT27" s="17"/>
-    </row>
-    <row r="28" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A28" s="19" t="s">
+      <c r="AQ27" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AU27" s="17"/>
+    </row>
+    <row r="28" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B28" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="5">
-        <f>SUM(F27:AP27)</f>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5">
+        <f>SUM(G27:AQ27)</f>
         <v>81</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="2"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -6351,107 +6469,107 @@
       <c r="AQ28" s="2"/>
       <c r="AR28" s="2"/>
       <c r="AS28" s="2"/>
-      <c r="AT28" s="20"/>
-    </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A30" s="1" t="s">
+      <c r="AT28" s="2"/>
+      <c r="AU28" s="20"/>
+    </row>
+    <row r="30" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T30" s="1" t="s">
+      <c r="U30" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="U30" s="1" t="s">
+      <c r="V30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Y30" s="1" t="s">
+      <c r="Z30" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="Z30" s="1" t="s">
+      <c r="AA30" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AN30" s="37" t="s">
+      <c r="AO30" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="AO30" s="38"/>
       <c r="AP30" s="38"/>
       <c r="AQ30" s="38"/>
       <c r="AR30" s="38"/>
       <c r="AS30" s="38"/>
-      <c r="AT30" s="39">
+      <c r="AT30" s="38"/>
+      <c r="AU30" s="39">
         <v>401.88</v>
       </c>
     </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T31" s="1" t="s">
+      <c r="U31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="U31" s="1" t="s">
+      <c r="V31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="Y31" s="1" t="s">
+      <c r="Z31" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Z31" s="1" t="s">
+      <c r="AA31" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AN31" s="40" t="s">
+      <c r="AO31" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="AO31" s="38"/>
       <c r="AP31" s="38"/>
       <c r="AQ31" s="38"/>
       <c r="AR31" s="38"/>
       <c r="AS31" s="38"/>
-      <c r="AT31" s="39" t="s">
+      <c r="AT31" s="38"/>
+      <c r="AU31" s="39" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B32" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="T32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="G34" s="29" t="s">
+    <row r="34" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="H34" s="29" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A35" s="9"/>
-      <c r="B35" s="3"/>
+    <row r="35" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B35" s="9"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="4"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="54" t="s">
+      <c r="H35" s="3"/>
+      <c r="I35" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="I35" s="54"/>
       <c r="J35" s="54"/>
       <c r="K35" s="54"/>
       <c r="L35" s="54"/>
@@ -6485,184 +6603,184 @@
       <c r="AN35" s="54"/>
       <c r="AO35" s="54"/>
       <c r="AP35" s="54"/>
-      <c r="AQ35" s="3"/>
+      <c r="AQ35" s="54"/>
       <c r="AR35" s="3"/>
       <c r="AS35" s="3"/>
-      <c r="AT35" s="10"/>
-    </row>
-    <row r="36" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A36" s="11" t="s">
+      <c r="AT35" s="3"/>
+      <c r="AU35" s="10"/>
+    </row>
+    <row r="36" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B36" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="L36" s="53" t="s">
+      <c r="F36" s="12"/>
+      <c r="M36" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="M36" s="53"/>
       <c r="N36" s="53"/>
       <c r="O36" s="53"/>
       <c r="P36" s="53"/>
       <c r="Q36" s="53"/>
       <c r="R36" s="53"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="53" t="s">
+      <c r="S36" s="53"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="U36" s="53"/>
       <c r="V36" s="53"/>
       <c r="W36" s="53"/>
       <c r="X36" s="53"/>
       <c r="Y36" s="53"/>
       <c r="Z36" s="53"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="53" t="s">
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="AC36" s="53"/>
       <c r="AD36" s="53"/>
       <c r="AE36" s="53"/>
       <c r="AF36" s="53"/>
       <c r="AG36" s="53"/>
       <c r="AH36" s="53"/>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="53" t="s">
+      <c r="AI36" s="53"/>
+      <c r="AJ36" s="30"/>
+      <c r="AK36" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="AK36" s="53"/>
       <c r="AL36" s="53"/>
       <c r="AM36" s="53"/>
       <c r="AN36" s="53"/>
       <c r="AO36" s="53"/>
       <c r="AP36" s="53"/>
-      <c r="AR36" s="55" t="s">
+      <c r="AQ36" s="53"/>
+      <c r="AS36" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="AS36" s="55"/>
-      <c r="AT36" s="56"/>
-    </row>
-    <row r="37" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A37" s="13" t="s">
+      <c r="AT36" s="55"/>
+      <c r="AU36" s="56"/>
+    </row>
+    <row r="37" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B37" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="6"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="7"/>
+      <c r="G37" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G37" s="41" t="s">
+      <c r="H37" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="I37" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="J37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="K37" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K37" s="6"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2" t="s">
+      <c r="L37" s="6"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O37" s="31" t="s">
+      <c r="P37" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="Q37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R37" s="2"/>
       <c r="S37" s="2"/>
-      <c r="T37" s="2" t="s">
+      <c r="T37" s="2"/>
+      <c r="U37" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="U37" s="2" t="s">
+      <c r="V37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="V37" s="2" t="s">
+      <c r="W37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="W37" s="31" t="s">
+      <c r="X37" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="X37" s="2" t="s">
+      <c r="Y37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Y37" s="2" t="s">
+      <c r="Z37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="Z37" s="2" t="s">
+      <c r="AA37" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AA37" s="2"/>
       <c r="AB37" s="2"/>
-      <c r="AC37" s="2" t="s">
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AD37" s="2" t="s">
+      <c r="AE37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AE37" s="31" t="s">
+      <c r="AF37" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="AF37" s="2" t="s">
+      <c r="AG37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AG37" s="2" t="s">
+      <c r="AH37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AH37" s="2"/>
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
-      <c r="AK37" s="2" t="s">
+      <c r="AK37" s="2"/>
+      <c r="AL37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AL37" s="2" t="s">
+      <c r="AM37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AM37" s="31" t="s">
+      <c r="AN37" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="AN37" s="2" t="s">
+      <c r="AO37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AO37" s="2" t="s">
+      <c r="AP37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AP37" s="2"/>
       <c r="AQ37" s="2"/>
-      <c r="AR37" s="6">
-        <v>1</v>
-      </c>
+      <c r="AR37" s="2"/>
       <c r="AS37" s="6">
+        <v>1</v>
+      </c>
+      <c r="AT37" s="6">
         <v>2</v>
       </c>
-      <c r="AT37" s="28" t="s">
+      <c r="AU37" s="28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A38" s="14" t="s">
+    <row r="38" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B38" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="48"/>
       <c r="C38" s="48"/>
-      <c r="D38" s="12"/>
+      <c r="D38" s="48"/>
       <c r="E38" s="12"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="16"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="43"/>
       <c r="I38" s="16"/>
       <c r="J38" s="16"/>
       <c r="K38" s="16"/>
@@ -6701,54 +6819,54 @@
       <c r="AR38" s="16"/>
       <c r="AS38" s="16"/>
       <c r="AT38" s="16"/>
-    </row>
-    <row r="39" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A39" s="11" t="s">
+      <c r="AU38" s="16"/>
+    </row>
+    <row r="39" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B39" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="1">
-        <f t="shared" ref="B39:B57" si="6">IF(C39=0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="8"/>
+      <c r="C39" s="1">
+        <f t="shared" ref="C39:C57" si="6">IF(D39=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="43"/>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
-      <c r="P39" s="47">
+      <c r="O39" s="8"/>
+      <c r="Q39" s="47">
         <v>15</v>
       </c>
-      <c r="Q39" s="47">
+      <c r="R39" s="47">
         <v>30</v>
       </c>
-      <c r="R39" s="8"/>
       <c r="S39" s="8"/>
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
-      <c r="V39" s="47">
+      <c r="V39" s="8"/>
+      <c r="W39" s="47">
         <v>20</v>
       </c>
-      <c r="W39" s="47"/>
-      <c r="X39" s="47">
+      <c r="X39" s="47"/>
+      <c r="Y39" s="47">
         <v>20</v>
       </c>
-      <c r="Y39" s="8"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
       <c r="AC39" s="8"/>
-      <c r="AD39" s="47">
+      <c r="AD39" s="8"/>
+      <c r="AE39" s="47">
         <v>20</v>
       </c>
-      <c r="AE39" s="8"/>
       <c r="AF39" s="8"/>
       <c r="AG39" s="8"/>
       <c r="AH39" s="8"/>
@@ -6757,34 +6875,34 @@
       <c r="AK39" s="8"/>
       <c r="AL39" s="8"/>
       <c r="AM39" s="8"/>
-      <c r="AN39" s="47">
+      <c r="AN39" s="8"/>
+      <c r="AO39" s="47">
         <v>30</v>
       </c>
-      <c r="AO39" s="8"/>
       <c r="AP39" s="8"/>
-      <c r="AR39" s="1" t="s">
+      <c r="AQ39" s="8"/>
+      <c r="AS39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AS39" s="1" t="s">
+      <c r="AT39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AT39" s="17"/>
-    </row>
-    <row r="40" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A40" s="11" t="s">
+      <c r="AU39" s="17"/>
+    </row>
+    <row r="40" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B40" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="1">
+      <c r="C40" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E40" s="12"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="8"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="43"/>
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
@@ -6819,23 +6937,23 @@
       <c r="AN40" s="8"/>
       <c r="AO40" s="8"/>
       <c r="AP40" s="8"/>
-      <c r="AT40" s="17"/>
-    </row>
-    <row r="41" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A41" s="11" t="s">
+      <c r="AQ40" s="8"/>
+      <c r="AU40" s="17"/>
+    </row>
+    <row r="41" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B41" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="1">
+      <c r="C41" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E41" s="12"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="8"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="43"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
@@ -6870,21 +6988,21 @@
       <c r="AN41" s="8"/>
       <c r="AO41" s="8"/>
       <c r="AP41" s="8"/>
-      <c r="AT41" s="17"/>
-    </row>
-    <row r="42" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A42" s="14" t="s">
+      <c r="AQ41" s="8"/>
+      <c r="AU41" s="17"/>
+    </row>
+    <row r="42" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="1">
+      <c r="C42" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D42" s="12"/>
       <c r="E42" s="12"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="8"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
@@ -6919,23 +7037,23 @@
       <c r="AN42" s="8"/>
       <c r="AO42" s="8"/>
       <c r="AP42" s="8"/>
-      <c r="AT42" s="17"/>
-    </row>
-    <row r="43" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A43" s="11" t="s">
+      <c r="AQ42" s="8"/>
+      <c r="AU42" s="17"/>
+    </row>
+    <row r="43" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B43" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="1">
+      <c r="C43" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="8"/>
+      <c r="E43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="43"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
@@ -6970,23 +7088,23 @@
       <c r="AN43" s="8"/>
       <c r="AO43" s="8"/>
       <c r="AP43" s="8"/>
-      <c r="AT43" s="17"/>
-    </row>
-    <row r="44" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A44" s="11" t="s">
+      <c r="AQ43" s="8"/>
+      <c r="AU43" s="17"/>
+    </row>
+    <row r="44" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B44" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="1">
+      <c r="C44" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E44" s="12"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="8"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="43"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
@@ -7021,21 +7139,21 @@
       <c r="AN44" s="8"/>
       <c r="AO44" s="8"/>
       <c r="AP44" s="8"/>
-      <c r="AT44" s="17"/>
-    </row>
-    <row r="45" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A45" s="14" t="s">
+      <c r="AQ44" s="8"/>
+      <c r="AU44" s="17"/>
+    </row>
+    <row r="45" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B45" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="1">
+      <c r="C45" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D45" s="12"/>
       <c r="E45" s="12"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="16"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="43"/>
       <c r="I45" s="16"/>
       <c r="J45" s="16"/>
       <c r="K45" s="16"/>
@@ -7074,22 +7192,22 @@
       <c r="AR45" s="16"/>
       <c r="AS45" s="16"/>
       <c r="AT45" s="16"/>
-    </row>
-    <row r="46" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A46" s="11" t="s">
+      <c r="AU45" s="16"/>
+    </row>
+    <row r="46" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B46" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="1">
+      <c r="C46" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="12"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="8"/>
+      <c r="E46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="43"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
@@ -7124,23 +7242,23 @@
       <c r="AN46" s="8"/>
       <c r="AO46" s="8"/>
       <c r="AP46" s="8"/>
-      <c r="AT46" s="17"/>
-    </row>
-    <row r="47" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A47" s="11" t="s">
+      <c r="AQ46" s="8"/>
+      <c r="AU46" s="17"/>
+    </row>
+    <row r="47" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B47" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="1">
+      <c r="C47" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="8"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="43"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
@@ -7175,20 +7293,20 @@
       <c r="AN47" s="8"/>
       <c r="AO47" s="8"/>
       <c r="AP47" s="8"/>
-      <c r="AT47" s="17"/>
-    </row>
-    <row r="48" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A48" s="18" t="s">
+      <c r="AQ47" s="8"/>
+      <c r="AU47" s="17"/>
+    </row>
+    <row r="48" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B48" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="1">
+      <c r="C48" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="E48" s="12"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="16"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="43"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="16"/>
@@ -7227,22 +7345,22 @@
       <c r="AR48" s="16"/>
       <c r="AS48" s="16"/>
       <c r="AT48" s="16"/>
-    </row>
-    <row r="49" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A49" s="11" t="s">
+      <c r="AU48" s="16"/>
+    </row>
+    <row r="49" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B49" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="1">
+      <c r="C49" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="12"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="8"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="43"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
@@ -7277,23 +7395,23 @@
       <c r="AN49" s="8"/>
       <c r="AO49" s="8"/>
       <c r="AP49" s="8"/>
-      <c r="AT49" s="17"/>
-    </row>
-    <row r="50" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A50" s="11" t="s">
+      <c r="AQ49" s="8"/>
+      <c r="AU49" s="17"/>
+    </row>
+    <row r="50" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B50" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="1">
+      <c r="C50" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E50" s="12"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="8"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="43"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
@@ -7315,7 +7433,7 @@
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
       <c r="AC50" s="8"/>
-      <c r="AH50" s="8"/>
+      <c r="AD50" s="8"/>
       <c r="AI50" s="8"/>
       <c r="AJ50" s="8"/>
       <c r="AK50" s="8"/>
@@ -7324,17 +7442,17 @@
       <c r="AN50" s="8"/>
       <c r="AO50" s="8"/>
       <c r="AP50" s="8"/>
-      <c r="AT50" s="17"/>
-    </row>
-    <row r="51" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A51" s="18" t="s">
+      <c r="AQ50" s="8"/>
+      <c r="AU50" s="17"/>
+    </row>
+    <row r="51" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B51" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B51" s="1">
+      <c r="C51" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="F51" s="8"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
@@ -7375,82 +7493,78 @@
       <c r="AR51" s="8"/>
       <c r="AS51" s="8"/>
       <c r="AT51" s="8"/>
-    </row>
-    <row r="52" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A52" s="11" t="s">
+      <c r="AU51" s="8"/>
+    </row>
+    <row r="52" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B52" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="1">
+      <c r="C52" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D52" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="58"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="59"/>
-      <c r="R52" s="59"/>
-      <c r="S52" s="59"/>
-      <c r="T52" s="59">
+      <c r="E52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="8">
         <v>30</v>
       </c>
-      <c r="U52" s="59">
+      <c r="V52" s="8">
         <v>20</v>
       </c>
-      <c r="V52" s="59">
+      <c r="W52" s="8">
         <v>10</v>
       </c>
-      <c r="W52" s="59"/>
-      <c r="X52" s="59">
+      <c r="X52" s="8"/>
+      <c r="Y52" s="8">
         <v>10</v>
       </c>
-      <c r="Y52" s="59"/>
-      <c r="Z52" s="59"/>
-      <c r="AA52" s="59"/>
-      <c r="AB52" s="59"/>
-      <c r="AC52" s="59"/>
-      <c r="AD52" s="59"/>
-      <c r="AE52" s="59"/>
-      <c r="AF52" s="59"/>
-      <c r="AG52" s="59"/>
-      <c r="AH52" s="59"/>
-      <c r="AI52" s="59"/>
-      <c r="AJ52" s="59"/>
-      <c r="AK52" s="59"/>
-      <c r="AL52" s="59"/>
-      <c r="AM52" s="59"/>
-      <c r="AN52" s="59"/>
-      <c r="AO52" s="59"/>
-      <c r="AP52" s="59"/>
-      <c r="AQ52" s="58"/>
-      <c r="AR52" s="58"/>
-      <c r="AS52" s="58"/>
-      <c r="AT52" s="60"/>
-    </row>
-    <row r="53" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A53" s="14" t="s">
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AB52" s="8"/>
+      <c r="AC52" s="8"/>
+      <c r="AD52" s="8"/>
+      <c r="AE52" s="8"/>
+      <c r="AF52" s="8"/>
+      <c r="AG52" s="8"/>
+      <c r="AH52" s="8"/>
+      <c r="AI52" s="8"/>
+      <c r="AJ52" s="8"/>
+      <c r="AK52" s="8"/>
+      <c r="AL52" s="8"/>
+      <c r="AM52" s="8"/>
+      <c r="AN52" s="8"/>
+      <c r="AO52" s="8"/>
+      <c r="AP52" s="8"/>
+      <c r="AQ52" s="8"/>
+      <c r="AU52" s="17"/>
+    </row>
+    <row r="53" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B53" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="1">
+      <c r="C53" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D53" s="12"/>
       <c r="E53" s="12"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="16"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="43"/>
       <c r="I53" s="16"/>
       <c r="J53" s="16"/>
       <c r="K53" s="16"/>
@@ -7485,307 +7599,304 @@
       <c r="AN53" s="16"/>
       <c r="AO53" s="16"/>
       <c r="AP53" s="16"/>
-      <c r="AQ53" s="12"/>
+      <c r="AQ53" s="16"/>
       <c r="AR53" s="12"/>
       <c r="AS53" s="12"/>
-      <c r="AT53" s="15"/>
-    </row>
-    <row r="54" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A54" s="11" t="s">
+      <c r="AT53" s="12"/>
+      <c r="AU53" s="15"/>
+    </row>
+    <row r="54" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B54" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="1">
+      <c r="C54" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="8" t="s">
-        <v>4</v>
-      </c>
+      <c r="E54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="43"/>
       <c r="I54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="J54" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="8"/>
+      <c r="K54" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="16"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="8"/>
+      <c r="S54" s="8"/>
+      <c r="T54" s="16"/>
       <c r="U54" s="8"/>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
-      <c r="X54" s="52">
+      <c r="X54" s="8"/>
+      <c r="Y54" s="52">
         <v>15</v>
       </c>
-      <c r="Y54" s="52">
+      <c r="Z54" s="52">
         <v>20</v>
       </c>
-      <c r="Z54" s="8"/>
-      <c r="AA54" s="16"/>
-      <c r="AB54" s="8"/>
+      <c r="AA54" s="8"/>
+      <c r="AB54" s="16"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
       <c r="AF54" s="8"/>
       <c r="AG54" s="8"/>
       <c r="AH54" s="8"/>
-      <c r="AI54" s="16"/>
-      <c r="AJ54" s="8"/>
+      <c r="AI54" s="8"/>
+      <c r="AJ54" s="16"/>
       <c r="AK54" s="8"/>
       <c r="AL54" s="8"/>
       <c r="AM54" s="8"/>
       <c r="AN54" s="8"/>
       <c r="AO54" s="8"/>
       <c r="AP54" s="8"/>
-      <c r="AQ54" s="12"/>
-      <c r="AT54" s="17"/>
-    </row>
-    <row r="55" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A55" s="11" t="s">
+      <c r="AQ54" s="8"/>
+      <c r="AR54" s="12"/>
+      <c r="AU54" s="17"/>
+    </row>
+    <row r="55" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B55" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="1">
+      <c r="C55" s="1">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E55" s="12"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="8"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="43"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="16"/>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
-      <c r="S55" s="16"/>
-      <c r="T55" s="8"/>
+      <c r="S55" s="8"/>
+      <c r="T55" s="16"/>
       <c r="U55" s="8"/>
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
-      <c r="Z55" s="8"/>
-      <c r="AA55" s="16"/>
-      <c r="AB55" s="8"/>
+      <c r="X55" s="8"/>
+      <c r="AA55" s="8"/>
+      <c r="AB55" s="16"/>
       <c r="AC55" s="8"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
       <c r="AF55" s="8"/>
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
-      <c r="AI55" s="16"/>
-      <c r="AJ55" s="8"/>
+      <c r="AI55" s="8"/>
+      <c r="AJ55" s="16"/>
       <c r="AK55" s="8"/>
       <c r="AL55" s="8"/>
       <c r="AM55" s="8"/>
       <c r="AN55" s="8"/>
       <c r="AO55" s="8"/>
       <c r="AP55" s="8"/>
-      <c r="AQ55" s="12"/>
-      <c r="AT55" s="17"/>
-    </row>
-    <row r="56" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A56" s="11" t="s">
+      <c r="AQ55" s="8"/>
+      <c r="AR55" s="12"/>
+      <c r="AU55" s="17"/>
+    </row>
+    <row r="56" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B56" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B56" s="1">
+      <c r="C56" s="1">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C56" s="1">
-        <f t="shared" ref="C52:C57" si="7">COUNTA(L56:AP56)</f>
+      <c r="D56" s="1">
+        <f t="shared" ref="D56:D57" si="7">COUNTA(M56:AQ56)</f>
         <v>2</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="8"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="43"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="16"/>
       <c r="M56" s="8"/>
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
       <c r="R56" s="8"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="8"/>
+      <c r="S56" s="8"/>
+      <c r="T56" s="16"/>
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
-      <c r="X56" s="36">
+      <c r="X56" s="8"/>
+      <c r="Y56" s="36">
         <v>10</v>
       </c>
-      <c r="Y56" s="36">
+      <c r="Z56" s="36">
         <v>20</v>
       </c>
-      <c r="Z56" s="8"/>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="8"/>
+      <c r="AA56" s="8"/>
+      <c r="AB56" s="16"/>
       <c r="AC56" s="8"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
-      <c r="AI56" s="16"/>
-      <c r="AJ56" s="8"/>
+      <c r="AI56" s="8"/>
+      <c r="AJ56" s="16"/>
       <c r="AK56" s="8"/>
       <c r="AL56" s="8"/>
       <c r="AM56" s="8"/>
       <c r="AN56" s="8"/>
       <c r="AO56" s="8"/>
       <c r="AP56" s="8"/>
-      <c r="AQ56" s="12"/>
-      <c r="AT56" s="17"/>
-    </row>
-    <row r="57" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A57" s="11" t="s">
+      <c r="AQ56" s="8"/>
+      <c r="AR56" s="12"/>
+      <c r="AU56" s="17"/>
+    </row>
+    <row r="57" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B57" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B57" s="1">
+      <c r="C57" s="1">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="C57" s="1">
+      <c r="D57" s="1">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="8"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="43"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="16"/>
       <c r="M57" s="8"/>
       <c r="N57" s="8"/>
       <c r="O57" s="8"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
       <c r="R57" s="8"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="8"/>
+      <c r="S57" s="8"/>
+      <c r="T57" s="16"/>
       <c r="U57" s="8"/>
       <c r="V57" s="8"/>
       <c r="W57" s="8"/>
-      <c r="X57" s="36">
+      <c r="X57" s="8"/>
+      <c r="Y57" s="36">
         <v>10</v>
       </c>
-      <c r="Y57" s="36">
+      <c r="Z57" s="36">
         <v>20</v>
       </c>
-      <c r="Z57" s="8"/>
-      <c r="AA57" s="16"/>
-      <c r="AB57" s="8"/>
+      <c r="AA57" s="8"/>
+      <c r="AB57" s="16"/>
       <c r="AC57" s="8"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
       <c r="AF57" s="8"/>
       <c r="AG57" s="8"/>
       <c r="AH57" s="8"/>
-      <c r="AI57" s="16"/>
-      <c r="AJ57" s="8"/>
+      <c r="AI57" s="8"/>
+      <c r="AJ57" s="16"/>
       <c r="AK57" s="8"/>
       <c r="AL57" s="8"/>
       <c r="AM57" s="8"/>
       <c r="AN57" s="8"/>
       <c r="AO57" s="8"/>
       <c r="AP57" s="8"/>
-      <c r="AQ57" s="12"/>
-      <c r="AT57" s="17"/>
-    </row>
-    <row r="58" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A58" s="19"/>
-      <c r="B58" s="2"/>
+      <c r="AQ57" s="8"/>
+      <c r="AR57" s="12"/>
+      <c r="AU57" s="17"/>
+    </row>
+    <row r="58" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B58" s="19"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="6"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="41"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="7"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
-      <c r="S58" s="7"/>
-      <c r="T58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="7"/>
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
       <c r="X58" s="6"/>
       <c r="Y58" s="6"/>
       <c r="Z58" s="6"/>
-      <c r="AA58" s="7"/>
-      <c r="AB58" s="6"/>
+      <c r="AA58" s="6"/>
+      <c r="AB58" s="7"/>
       <c r="AC58" s="6"/>
       <c r="AD58" s="6"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="6"/>
       <c r="AG58" s="6"/>
       <c r="AH58" s="6"/>
-      <c r="AI58" s="7"/>
-      <c r="AJ58" s="6"/>
+      <c r="AI58" s="6"/>
+      <c r="AJ58" s="7"/>
       <c r="AK58" s="6"/>
       <c r="AL58" s="6"/>
       <c r="AM58" s="6"/>
       <c r="AN58" s="6"/>
       <c r="AO58" s="6"/>
       <c r="AP58" s="6"/>
-      <c r="AQ58" s="5"/>
-      <c r="AR58" s="2"/>
+      <c r="AQ58" s="6"/>
+      <c r="AR58" s="5"/>
       <c r="AS58" s="2"/>
-      <c r="AT58" s="20"/>
-    </row>
-    <row r="59" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A59" s="11" t="s">
+      <c r="AT58" s="2"/>
+      <c r="AU58" s="20"/>
+    </row>
+    <row r="59" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B59" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E59" s="12"/>
-      <c r="F59" s="1">
-        <f>COUNTA(F38:F58)</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="42">
+      <c r="F59" s="12"/>
+      <c r="G59" s="1">
         <f>COUNTA(G38:G58)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="42">
         <f>COUNTA(H38:H58)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="1">
         <f>COUNTA(I38:I58)</f>
@@ -7795,13 +7906,13 @@
         <f>COUNTA(J38:J58)</f>
         <v>1</v>
       </c>
-      <c r="K59" s="12"/>
-      <c r="L59" s="1">
-        <f t="shared" ref="L59:R59" si="8">COUNTA(L38:L58)</f>
-        <v>0</v>
-      </c>
+      <c r="K59" s="1">
+        <f>COUNTA(K38:K58)</f>
+        <v>1</v>
+      </c>
+      <c r="L59" s="12"/>
       <c r="M59" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="M59:S59" si="8">COUNTA(M38:M58)</f>
         <v>0</v>
       </c>
       <c r="N59" s="1">
@@ -7814,7 +7925,7 @@
       </c>
       <c r="P59" s="1">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="1">
         <f t="shared" si="8"/>
@@ -7822,53 +7933,53 @@
       </c>
       <c r="R59" s="1">
         <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S59" s="1">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S59" s="12"/>
-      <c r="T59" s="1">
-        <f t="shared" ref="T59:Z59" si="9">COUNTA(T38:T58)</f>
-        <v>1</v>
-      </c>
+      <c r="T59" s="12"/>
       <c r="U59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="U59:AA59" si="9">COUNTA(U38:U58)</f>
         <v>1</v>
       </c>
       <c r="V59" s="1">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W59" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X59" s="1">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="1">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z59" s="1">
         <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="AA59" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="12"/>
-      <c r="AB59" s="1">
-        <f t="shared" ref="AB59:AH59" si="10">COUNTA(AB38:AB58)</f>
+      <c r="AB59" s="12"/>
+      <c r="AC59" s="1">
+        <f t="shared" ref="AC59:AI59" si="10">COUNTA(AC38:AC58)</f>
         <v>0</v>
       </c>
-      <c r="AC59" s="1">
+      <c r="AD59" s="1">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AD59" s="1">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
       <c r="AE59" s="1">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF59" s="1">
         <f t="shared" si="10"/>
@@ -7882,13 +7993,13 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AI59" s="12"/>
-      <c r="AJ59" s="1">
-        <f t="shared" ref="AJ59:AO59" si="11">COUNTA(AJ38:AJ58)</f>
+      <c r="AI59" s="1">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
+      <c r="AJ59" s="12"/>
       <c r="AK59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="AK59:AQ59" si="11">COUNTA(AK38:AK58)</f>
         <v>0</v>
       </c>
       <c r="AL59" s="1">
@@ -7901,101 +8012,105 @@
       </c>
       <c r="AN59" s="1">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO59" s="1">
         <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AP59" s="1">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AP59" s="1">
-        <f t="shared" ref="AP59" si="12">COUNTA(AP38:AP58)</f>
+      <c r="AQ59" s="1">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AQ59" s="12"/>
-      <c r="AT59" s="17"/>
-    </row>
-    <row r="60" spans="1:46" x14ac:dyDescent="0.15">
-      <c r="A60" s="19" t="s">
+      <c r="AR59" s="12"/>
+      <c r="AU59" s="17"/>
+    </row>
+    <row r="60" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B60" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="5">
-        <f>SUM(F59:AP59)</f>
+      <c r="D60" s="2"/>
+      <c r="E60" s="5">
+        <f>SUM(G59:AQ59)</f>
         <v>19</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="2"/>
+      <c r="F60" s="5"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="5"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
-      <c r="S60" s="5"/>
-      <c r="T60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="5"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2"/>
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
-      <c r="AA60" s="5"/>
-      <c r="AB60" s="2"/>
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="5"/>
       <c r="AC60" s="2"/>
       <c r="AD60" s="2"/>
       <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
-      <c r="AI60" s="5"/>
-      <c r="AJ60" s="2"/>
+      <c r="AI60" s="2"/>
+      <c r="AJ60" s="5"/>
       <c r="AK60" s="2"/>
       <c r="AL60" s="2"/>
       <c r="AM60" s="2"/>
       <c r="AN60" s="2"/>
       <c r="AO60" s="2"/>
       <c r="AP60" s="2"/>
-      <c r="AQ60" s="5"/>
-      <c r="AR60" s="2"/>
+      <c r="AQ60" s="2"/>
+      <c r="AR60" s="5"/>
       <c r="AS60" s="2"/>
-      <c r="AT60" s="20"/>
+      <c r="AT60" s="2"/>
+      <c r="AU60" s="20"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="AT30:AT31" name="Range1"/>
+    <protectedRange sqref="AU30:AU31" name="Range1"/>
   </protectedRanges>
   <mergeCells count="12">
-    <mergeCell ref="L3:R3"/>
-    <mergeCell ref="H2:AP2"/>
-    <mergeCell ref="AR36:AT36"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AJ3:AP3"/>
-    <mergeCell ref="AB3:AH3"/>
-    <mergeCell ref="T3:Z3"/>
-    <mergeCell ref="H35:AP35"/>
-    <mergeCell ref="L36:R36"/>
-    <mergeCell ref="T36:Z36"/>
-    <mergeCell ref="AB36:AH36"/>
-    <mergeCell ref="AJ36:AP36"/>
+    <mergeCell ref="I35:AQ35"/>
+    <mergeCell ref="M36:S36"/>
+    <mergeCell ref="U36:AA36"/>
+    <mergeCell ref="AC36:AI36"/>
+    <mergeCell ref="AK36:AQ36"/>
+    <mergeCell ref="AS36:AU36"/>
+    <mergeCell ref="I2:AQ2"/>
+    <mergeCell ref="M3:S3"/>
+    <mergeCell ref="U3:AA3"/>
+    <mergeCell ref="AC3:AI3"/>
+    <mergeCell ref="AK3:AQ3"/>
+    <mergeCell ref="AS3:AU3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B58:C60 B26:C38 B6:B25 B39:B57">
+  <conditionalFormatting sqref="C6:C25 C26:D38 C39:C57 C58:D60">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:C25">
+  <conditionalFormatting sqref="D14:D25">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39:C57">
+  <conditionalFormatting sqref="D39:D57">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -8011,6 +8126,3387 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AU60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" style="1"/>
+    <col min="2" max="2" width="29.5" style="1" customWidth="1"/>
+    <col min="3" max="4" width="6.5" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" style="1" customWidth="1"/>
+    <col min="7" max="11" width="4.5" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="0.83203125" style="1" customWidth="1"/>
+    <col min="13" max="19" width="3.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="0.6640625" style="1" customWidth="1"/>
+    <col min="21" max="27" width="3.5" style="1" customWidth="1"/>
+    <col min="28" max="28" width="0.6640625" style="1" customWidth="1"/>
+    <col min="29" max="35" width="3.5" style="1" customWidth="1"/>
+    <col min="36" max="36" width="1.1640625" style="1" customWidth="1"/>
+    <col min="37" max="43" width="3.5" style="1" customWidth="1"/>
+    <col min="44" max="44" width="0.83203125" style="1" customWidth="1"/>
+    <col min="45" max="47" width="4.5" style="1" customWidth="1"/>
+    <col min="48" max="16384" width="9.1640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="9"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="54"/>
+      <c r="AH2" s="54"/>
+      <c r="AI2" s="54"/>
+      <c r="AJ2" s="54"/>
+      <c r="AK2" s="54"/>
+      <c r="AL2" s="54"/>
+      <c r="AM2" s="54"/>
+      <c r="AN2" s="54"/>
+      <c r="AO2" s="54"/>
+      <c r="AP2" s="54"/>
+      <c r="AQ2" s="54"/>
+      <c r="AR2" s="4"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="10"/>
+    </row>
+    <row r="3" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53"/>
+      <c r="AN3" s="53"/>
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="53"/>
+      <c r="AQ3" s="53"/>
+      <c r="AR3" s="12"/>
+      <c r="AS3" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT3" s="55"/>
+      <c r="AU3" s="56"/>
+    </row>
+    <row r="4" spans="1:47" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="49"/>
+      <c r="E4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S4" s="2"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="X4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="6">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="12"/>
+      <c r="AN5" s="12"/>
+      <c r="AO5" s="12"/>
+      <c r="AP5" s="12"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="12"/>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="12"/>
+      <c r="AU5" s="15"/>
+    </row>
+    <row r="6" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" ref="C6:C25" si="0">IF(D6=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="43"/>
+      <c r="I6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="47">
+        <v>10</v>
+      </c>
+      <c r="X6" s="47">
+        <v>15</v>
+      </c>
+      <c r="Y6" s="47">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8"/>
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8"/>
+      <c r="AF6" s="47">
+        <v>20</v>
+      </c>
+      <c r="AG6" s="47">
+        <v>20</v>
+      </c>
+      <c r="AH6" s="8"/>
+      <c r="AI6" s="8"/>
+      <c r="AJ6" s="8"/>
+      <c r="AK6" s="8"/>
+      <c r="AL6" s="8"/>
+      <c r="AM6" s="47">
+        <v>20</v>
+      </c>
+      <c r="AN6" s="47">
+        <v>10</v>
+      </c>
+      <c r="AO6" s="8"/>
+      <c r="AP6" s="8"/>
+      <c r="AQ6" s="8"/>
+      <c r="AS6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU6" s="17"/>
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="8"/>
+      <c r="AU7" s="17"/>
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="47">
+        <v>15</v>
+      </c>
+      <c r="X8" s="47">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="47">
+        <v>15</v>
+      </c>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AU8" s="17"/>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="16"/>
+      <c r="AM9" s="16"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="16"/>
+      <c r="AP9" s="16"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="16"/>
+      <c r="AS9" s="16"/>
+      <c r="AT9" s="16"/>
+      <c r="AU9" s="16"/>
+    </row>
+    <row r="10" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="43"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+      <c r="AU10" s="17"/>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="47">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="47">
+        <v>30</v>
+      </c>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="47">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8"/>
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+      <c r="AH11" s="8"/>
+      <c r="AI11" s="8"/>
+      <c r="AJ11" s="8"/>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
+      <c r="AU11" s="17"/>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B12" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+      <c r="AM12" s="16"/>
+      <c r="AN12" s="16"/>
+      <c r="AO12" s="16"/>
+      <c r="AP12" s="16"/>
+      <c r="AQ12" s="16"/>
+      <c r="AR12" s="16"/>
+      <c r="AS12" s="16"/>
+      <c r="AT12" s="16"/>
+      <c r="AU12" s="16"/>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
+      <c r="AU13" s="17"/>
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="47">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="47">
+        <v>20</v>
+      </c>
+      <c r="AH14" s="8"/>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="8"/>
+      <c r="AQ14" s="8"/>
+      <c r="AU14" s="17"/>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B15" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="16"/>
+      <c r="AI15" s="16"/>
+      <c r="AJ15" s="16"/>
+      <c r="AK15" s="16"/>
+      <c r="AL15" s="16"/>
+      <c r="AM15" s="16"/>
+      <c r="AN15" s="16"/>
+      <c r="AO15" s="16"/>
+      <c r="AP15" s="16"/>
+      <c r="AQ15" s="16"/>
+      <c r="AR15" s="16"/>
+      <c r="AS15" s="16"/>
+      <c r="AT15" s="16"/>
+      <c r="AU15" s="16"/>
+    </row>
+    <row r="16" spans="1:47" x14ac:dyDescent="0.15">
+      <c r="B16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="47">
+        <v>10</v>
+      </c>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8"/>
+      <c r="AD16" s="8"/>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AH16" s="8"/>
+      <c r="AI16" s="8"/>
+      <c r="AJ16" s="8"/>
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="47">
+        <v>10</v>
+      </c>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="47">
+        <v>10</v>
+      </c>
+      <c r="AP16" s="8"/>
+      <c r="AQ16" s="8"/>
+      <c r="AU16" s="17"/>
+    </row>
+    <row r="17" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B17" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="47">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="47">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="47">
+        <v>20</v>
+      </c>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="47">
+        <v>20</v>
+      </c>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="47">
+        <v>10</v>
+      </c>
+      <c r="AO17" s="47">
+        <v>10</v>
+      </c>
+      <c r="AP17" s="8"/>
+      <c r="AQ17" s="8"/>
+      <c r="AU17" s="17"/>
+    </row>
+    <row r="18" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B18" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="8"/>
+      <c r="AD18" s="8"/>
+      <c r="AE18" s="8"/>
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="8"/>
+      <c r="AI18" s="8"/>
+      <c r="AJ18" s="8"/>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="AQ18" s="8"/>
+      <c r="AR18" s="8"/>
+      <c r="AS18" s="33"/>
+      <c r="AT18" s="8"/>
+      <c r="AU18" s="8"/>
+    </row>
+    <row r="19" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B19" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="47">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="50">
+        <v>30</v>
+      </c>
+      <c r="V19" s="50">
+        <v>20</v>
+      </c>
+      <c r="W19" s="50">
+        <v>10</v>
+      </c>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="50">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8"/>
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="50">
+        <v>10</v>
+      </c>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AQ19" s="8"/>
+      <c r="AS19" s="8"/>
+      <c r="AU19" s="17"/>
+    </row>
+    <row r="20" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
+      <c r="AK20" s="16"/>
+      <c r="AL20" s="16"/>
+      <c r="AM20" s="16"/>
+      <c r="AN20" s="16"/>
+      <c r="AO20" s="16"/>
+      <c r="AP20" s="16"/>
+      <c r="AQ20" s="16"/>
+      <c r="AR20" s="16"/>
+      <c r="AS20" s="8"/>
+      <c r="AT20" s="16"/>
+      <c r="AU20" s="16"/>
+    </row>
+    <row r="21" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="43"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
+      <c r="AE21" s="8"/>
+      <c r="AF21" s="8"/>
+      <c r="AG21" s="8"/>
+      <c r="AH21" s="8"/>
+      <c r="AI21" s="8"/>
+      <c r="AJ21" s="8"/>
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="8"/>
+      <c r="AN21" s="8"/>
+      <c r="AO21" s="8"/>
+      <c r="AP21" s="8"/>
+      <c r="AQ21" s="8"/>
+      <c r="AU21" s="17"/>
+    </row>
+    <row r="22" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B22" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="52">
+        <v>15</v>
+      </c>
+      <c r="Z22" s="52">
+        <v>20</v>
+      </c>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="8"/>
+      <c r="AF22" s="8"/>
+      <c r="AG22" s="8"/>
+      <c r="AH22" s="8"/>
+      <c r="AI22" s="8"/>
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="52">
+        <v>20</v>
+      </c>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="52">
+        <v>20</v>
+      </c>
+      <c r="AP22" s="8"/>
+      <c r="AQ22" s="8"/>
+      <c r="AU22" s="17"/>
+    </row>
+    <row r="23" spans="2:47" s="32" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="AA23" s="51"/>
+      <c r="AB23" s="33"/>
+      <c r="AC23" s="33"/>
+      <c r="AD23" s="33"/>
+      <c r="AE23" s="33"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="51">
+        <v>10</v>
+      </c>
+      <c r="AH23" s="51">
+        <v>20</v>
+      </c>
+      <c r="AI23" s="33"/>
+      <c r="AJ23" s="33"/>
+      <c r="AK23" s="33"/>
+      <c r="AL23" s="33"/>
+      <c r="AM23" s="33">
+        <v>20</v>
+      </c>
+      <c r="AN23" s="33"/>
+      <c r="AO23" s="33">
+        <v>20</v>
+      </c>
+      <c r="AQ23" s="33"/>
+      <c r="AU23" s="35"/>
+    </row>
+    <row r="24" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" ref="D24:D25" si="1">COUNTA(M24:AQ24)</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="36">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="36">
+        <v>20</v>
+      </c>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="8"/>
+      <c r="AE24" s="8"/>
+      <c r="AF24" s="8"/>
+      <c r="AG24" s="36">
+        <v>10</v>
+      </c>
+      <c r="AH24" s="36">
+        <v>20</v>
+      </c>
+      <c r="AI24" s="8"/>
+      <c r="AJ24" s="8"/>
+      <c r="AK24" s="8"/>
+      <c r="AL24" s="8"/>
+      <c r="AM24" s="8">
+        <v>20</v>
+      </c>
+      <c r="AN24" s="8"/>
+      <c r="AO24" s="8">
+        <v>20</v>
+      </c>
+      <c r="AQ24" s="8"/>
+      <c r="AU24" s="17"/>
+    </row>
+    <row r="25" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B25" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="36">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="36">
+        <v>20</v>
+      </c>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8"/>
+      <c r="AF25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="8"/>
+      <c r="AI25" s="8"/>
+      <c r="AJ25" s="8"/>
+      <c r="AK25" s="8"/>
+      <c r="AL25" s="8"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
+      <c r="AQ25" s="8"/>
+      <c r="AU25" s="17"/>
+    </row>
+    <row r="26" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B26" s="19"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="6"/>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="6"/>
+      <c r="AL26" s="6"/>
+      <c r="AM26" s="6"/>
+      <c r="AN26" s="6"/>
+      <c r="AO26" s="6"/>
+      <c r="AP26" s="6"/>
+      <c r="AQ26" s="6"/>
+      <c r="AR26" s="2"/>
+      <c r="AS26" s="2"/>
+      <c r="AT26" s="2"/>
+      <c r="AU26" s="20"/>
+    </row>
+    <row r="27" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B27" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="1">
+        <f>COUNTA(G5:G26)</f>
+        <v>6</v>
+      </c>
+      <c r="H27" s="42">
+        <f>COUNTA(H5:H26)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <f>COUNTA(I5:I26)</f>
+        <v>6</v>
+      </c>
+      <c r="J27" s="1">
+        <f>COUNTA(J5:J26)</f>
+        <v>11</v>
+      </c>
+      <c r="K27" s="1">
+        <f>COUNTA(K5:K26)</f>
+        <v>10</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" ref="M27:S27" si="2">COUNTA(M5:M26)</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Q27" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="1">
+        <f t="shared" ref="U27:AA27" si="3">COUNTA(U5:U26)</f>
+        <v>1</v>
+      </c>
+      <c r="V27" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="W27" s="1">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="X27" s="1">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="Y27" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="Z27" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AA27" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="1">
+        <f t="shared" ref="AC27:AI27" si="4">COUNTA(AC5:AC26)</f>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AF27" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AG27" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AH27" s="1">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AI27" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK27" s="1">
+        <f t="shared" ref="AK27:AQ27" si="5">COUNTA(AK5:AK26)</f>
+        <v>0</v>
+      </c>
+      <c r="AL27" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM27" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AN27" s="1">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AO27" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AP27" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AU27" s="17"/>
+    </row>
+    <row r="28" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B28" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5">
+        <f>SUM(G27:AQ27)</f>
+        <v>81</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
+      <c r="AM28" s="2"/>
+      <c r="AN28" s="2"/>
+      <c r="AO28" s="2"/>
+      <c r="AP28" s="2"/>
+      <c r="AQ28" s="2"/>
+      <c r="AR28" s="2"/>
+      <c r="AS28" s="2"/>
+      <c r="AT28" s="2"/>
+      <c r="AU28" s="20"/>
+    </row>
+    <row r="30" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO30" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP30" s="38"/>
+      <c r="AQ30" s="38"/>
+      <c r="AR30" s="38"/>
+      <c r="AS30" s="38"/>
+      <c r="AT30" s="38"/>
+      <c r="AU30" s="39">
+        <v>401.88</v>
+      </c>
+    </row>
+    <row r="31" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO31" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="AP31" s="38"/>
+      <c r="AQ31" s="38"/>
+      <c r="AR31" s="38"/>
+      <c r="AS31" s="38"/>
+      <c r="AT31" s="38"/>
+      <c r="AU31" s="39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="H34" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B35" s="9"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="54"/>
+      <c r="V35" s="54"/>
+      <c r="W35" s="54"/>
+      <c r="X35" s="54"/>
+      <c r="Y35" s="54"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="54"/>
+      <c r="AB35" s="54"/>
+      <c r="AC35" s="54"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="54"/>
+      <c r="AF35" s="54"/>
+      <c r="AG35" s="54"/>
+      <c r="AH35" s="54"/>
+      <c r="AI35" s="54"/>
+      <c r="AJ35" s="54"/>
+      <c r="AK35" s="54"/>
+      <c r="AL35" s="54"/>
+      <c r="AM35" s="54"/>
+      <c r="AN35" s="54"/>
+      <c r="AO35" s="54"/>
+      <c r="AP35" s="54"/>
+      <c r="AQ35" s="54"/>
+      <c r="AR35" s="3"/>
+      <c r="AS35" s="3"/>
+      <c r="AT35" s="3"/>
+      <c r="AU35" s="10"/>
+    </row>
+    <row r="36" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="M36" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="53"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="53"/>
+      <c r="AF36" s="53"/>
+      <c r="AG36" s="53"/>
+      <c r="AH36" s="53"/>
+      <c r="AI36" s="53"/>
+      <c r="AJ36" s="30"/>
+      <c r="AK36" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL36" s="53"/>
+      <c r="AM36" s="53"/>
+      <c r="AN36" s="53"/>
+      <c r="AO36" s="53"/>
+      <c r="AP36" s="53"/>
+      <c r="AQ36" s="53"/>
+      <c r="AS36" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT36" s="55"/>
+      <c r="AU36" s="56"/>
+    </row>
+    <row r="37" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B37" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H37" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="L37" s="6"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="P37" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X37" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB37" s="2"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF37" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI37" s="2"/>
+      <c r="AJ37" s="2"/>
+      <c r="AK37" s="2"/>
+      <c r="AL37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN37" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ37" s="2"/>
+      <c r="AR37" s="2"/>
+      <c r="AS37" s="6">
+        <v>1</v>
+      </c>
+      <c r="AT37" s="6">
+        <v>2</v>
+      </c>
+      <c r="AU37" s="28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B38" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="16"/>
+      <c r="Y38" s="16"/>
+      <c r="Z38" s="16"/>
+      <c r="AA38" s="16"/>
+      <c r="AB38" s="16"/>
+      <c r="AC38" s="16"/>
+      <c r="AD38" s="16"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="16"/>
+      <c r="AI38" s="16"/>
+      <c r="AJ38" s="16"/>
+      <c r="AK38" s="16"/>
+      <c r="AL38" s="16"/>
+      <c r="AM38" s="16"/>
+      <c r="AN38" s="16"/>
+      <c r="AO38" s="16"/>
+      <c r="AP38" s="16"/>
+      <c r="AQ38" s="16"/>
+      <c r="AR38" s="16"/>
+      <c r="AS38" s="16"/>
+      <c r="AT38" s="16"/>
+      <c r="AU38" s="16"/>
+    </row>
+    <row r="39" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B39" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" ref="C39:C57" si="6">IF(D39=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="Q39" s="47">
+        <v>15</v>
+      </c>
+      <c r="R39" s="47">
+        <v>30</v>
+      </c>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
+      <c r="V39" s="8"/>
+      <c r="W39" s="47">
+        <v>20</v>
+      </c>
+      <c r="X39" s="47"/>
+      <c r="Y39" s="47">
+        <v>20</v>
+      </c>
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AB39" s="8"/>
+      <c r="AC39" s="8"/>
+      <c r="AD39" s="8"/>
+      <c r="AE39" s="47">
+        <v>20</v>
+      </c>
+      <c r="AF39" s="8"/>
+      <c r="AG39" s="8"/>
+      <c r="AH39" s="8"/>
+      <c r="AI39" s="8"/>
+      <c r="AJ39" s="8"/>
+      <c r="AK39" s="8"/>
+      <c r="AL39" s="8"/>
+      <c r="AM39" s="8"/>
+      <c r="AN39" s="8"/>
+      <c r="AO39" s="47">
+        <v>30</v>
+      </c>
+      <c r="AP39" s="8"/>
+      <c r="AQ39" s="8"/>
+      <c r="AS39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU39" s="17"/>
+    </row>
+    <row r="40" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B40" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8"/>
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8"/>
+      <c r="AA40" s="8"/>
+      <c r="AB40" s="8"/>
+      <c r="AC40" s="8"/>
+      <c r="AD40" s="8"/>
+      <c r="AE40" s="8"/>
+      <c r="AF40" s="8"/>
+      <c r="AG40" s="8"/>
+      <c r="AH40" s="8"/>
+      <c r="AI40" s="8"/>
+      <c r="AJ40" s="8"/>
+      <c r="AK40" s="8"/>
+      <c r="AL40" s="8"/>
+      <c r="AM40" s="8"/>
+      <c r="AN40" s="8"/>
+      <c r="AO40" s="8"/>
+      <c r="AP40" s="8"/>
+      <c r="AQ40" s="8"/>
+      <c r="AU40" s="17"/>
+    </row>
+    <row r="41" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B41" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="8"/>
+      <c r="V41" s="8"/>
+      <c r="W41" s="8"/>
+      <c r="X41" s="8"/>
+      <c r="Y41" s="8"/>
+      <c r="Z41" s="8"/>
+      <c r="AA41" s="8"/>
+      <c r="AB41" s="8"/>
+      <c r="AC41" s="8"/>
+      <c r="AD41" s="8"/>
+      <c r="AE41" s="8"/>
+      <c r="AF41" s="8"/>
+      <c r="AG41" s="8"/>
+      <c r="AH41" s="8"/>
+      <c r="AI41" s="8"/>
+      <c r="AJ41" s="8"/>
+      <c r="AK41" s="8"/>
+      <c r="AL41" s="8"/>
+      <c r="AM41" s="8"/>
+      <c r="AN41" s="8"/>
+      <c r="AO41" s="8"/>
+      <c r="AP41" s="8"/>
+      <c r="AQ41" s="8"/>
+      <c r="AU41" s="17"/>
+    </row>
+    <row r="42" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="8"/>
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8"/>
+      <c r="V42" s="8"/>
+      <c r="W42" s="8"/>
+      <c r="X42" s="8"/>
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="8"/>
+      <c r="AA42" s="8"/>
+      <c r="AB42" s="8"/>
+      <c r="AC42" s="8"/>
+      <c r="AD42" s="8"/>
+      <c r="AE42" s="8"/>
+      <c r="AF42" s="8"/>
+      <c r="AG42" s="8"/>
+      <c r="AH42" s="8"/>
+      <c r="AI42" s="8"/>
+      <c r="AJ42" s="8"/>
+      <c r="AK42" s="8"/>
+      <c r="AL42" s="8"/>
+      <c r="AM42" s="8"/>
+      <c r="AN42" s="8"/>
+      <c r="AO42" s="8"/>
+      <c r="AP42" s="8"/>
+      <c r="AQ42" s="8"/>
+      <c r="AU42" s="17"/>
+    </row>
+    <row r="43" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B43" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="8"/>
+      <c r="S43" s="8"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="8"/>
+      <c r="V43" s="8"/>
+      <c r="W43" s="8"/>
+      <c r="X43" s="8"/>
+      <c r="Y43" s="8"/>
+      <c r="Z43" s="8"/>
+      <c r="AA43" s="8"/>
+      <c r="AB43" s="8"/>
+      <c r="AC43" s="8"/>
+      <c r="AD43" s="8"/>
+      <c r="AE43" s="8"/>
+      <c r="AF43" s="8"/>
+      <c r="AG43" s="8"/>
+      <c r="AH43" s="8"/>
+      <c r="AI43" s="8"/>
+      <c r="AJ43" s="8"/>
+      <c r="AK43" s="8"/>
+      <c r="AL43" s="8"/>
+      <c r="AM43" s="8"/>
+      <c r="AN43" s="8"/>
+      <c r="AO43" s="8"/>
+      <c r="AP43" s="8"/>
+      <c r="AQ43" s="8"/>
+      <c r="AU43" s="17"/>
+    </row>
+    <row r="44" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="8"/>
+      <c r="S44" s="8"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="8"/>
+      <c r="V44" s="8"/>
+      <c r="W44" s="8"/>
+      <c r="X44" s="8"/>
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="8"/>
+      <c r="AA44" s="8"/>
+      <c r="AB44" s="8"/>
+      <c r="AC44" s="8"/>
+      <c r="AD44" s="8"/>
+      <c r="AE44" s="8"/>
+      <c r="AF44" s="8"/>
+      <c r="AG44" s="8"/>
+      <c r="AH44" s="8"/>
+      <c r="AI44" s="8"/>
+      <c r="AJ44" s="8"/>
+      <c r="AK44" s="8"/>
+      <c r="AL44" s="8"/>
+      <c r="AM44" s="8"/>
+      <c r="AN44" s="8"/>
+      <c r="AO44" s="8"/>
+      <c r="AP44" s="8"/>
+      <c r="AQ44" s="8"/>
+      <c r="AU44" s="17"/>
+    </row>
+    <row r="45" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B45" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+      <c r="AF45" s="16"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="16"/>
+      <c r="AI45" s="16"/>
+      <c r="AJ45" s="16"/>
+      <c r="AK45" s="16"/>
+      <c r="AL45" s="16"/>
+      <c r="AM45" s="16"/>
+      <c r="AN45" s="16"/>
+      <c r="AO45" s="16"/>
+      <c r="AP45" s="16"/>
+      <c r="AQ45" s="16"/>
+      <c r="AR45" s="16"/>
+      <c r="AS45" s="16"/>
+      <c r="AT45" s="16"/>
+      <c r="AU45" s="16"/>
+    </row>
+    <row r="46" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="8"/>
+      <c r="X46" s="8"/>
+      <c r="Y46" s="8"/>
+      <c r="Z46" s="8"/>
+      <c r="AA46" s="8"/>
+      <c r="AB46" s="8"/>
+      <c r="AC46" s="8"/>
+      <c r="AD46" s="8"/>
+      <c r="AE46" s="8"/>
+      <c r="AF46" s="8"/>
+      <c r="AG46" s="8"/>
+      <c r="AH46" s="8"/>
+      <c r="AI46" s="8"/>
+      <c r="AJ46" s="8"/>
+      <c r="AK46" s="8"/>
+      <c r="AL46" s="8"/>
+      <c r="AM46" s="8"/>
+      <c r="AN46" s="8"/>
+      <c r="AO46" s="8"/>
+      <c r="AP46" s="8"/>
+      <c r="AQ46" s="8"/>
+      <c r="AU46" s="17"/>
+    </row>
+    <row r="47" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B47" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8"/>
+      <c r="S47" s="8"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="8"/>
+      <c r="V47" s="8"/>
+      <c r="W47" s="8"/>
+      <c r="X47" s="8"/>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AB47" s="8"/>
+      <c r="AC47" s="8"/>
+      <c r="AD47" s="8"/>
+      <c r="AE47" s="8"/>
+      <c r="AF47" s="8"/>
+      <c r="AG47" s="8"/>
+      <c r="AH47" s="8"/>
+      <c r="AI47" s="8"/>
+      <c r="AJ47" s="8"/>
+      <c r="AK47" s="8"/>
+      <c r="AL47" s="8"/>
+      <c r="AM47" s="8"/>
+      <c r="AN47" s="8"/>
+      <c r="AO47" s="8"/>
+      <c r="AP47" s="8"/>
+      <c r="AQ47" s="8"/>
+      <c r="AU47" s="17"/>
+    </row>
+    <row r="48" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B48" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="16"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="16"/>
+      <c r="AI48" s="16"/>
+      <c r="AJ48" s="16"/>
+      <c r="AK48" s="16"/>
+      <c r="AL48" s="16"/>
+      <c r="AM48" s="16"/>
+      <c r="AN48" s="16"/>
+      <c r="AO48" s="16"/>
+      <c r="AP48" s="16"/>
+      <c r="AQ48" s="16"/>
+      <c r="AR48" s="16"/>
+      <c r="AS48" s="16"/>
+      <c r="AT48" s="16"/>
+      <c r="AU48" s="16"/>
+    </row>
+    <row r="49" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B49" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
+      <c r="Q49" s="8"/>
+      <c r="R49" s="8"/>
+      <c r="S49" s="8"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="8"/>
+      <c r="V49" s="8"/>
+      <c r="W49" s="8"/>
+      <c r="X49" s="8"/>
+      <c r="Y49" s="8"/>
+      <c r="Z49" s="8"/>
+      <c r="AA49" s="8"/>
+      <c r="AB49" s="8"/>
+      <c r="AC49" s="8"/>
+      <c r="AD49" s="8"/>
+      <c r="AE49" s="8"/>
+      <c r="AF49" s="8"/>
+      <c r="AG49" s="8"/>
+      <c r="AH49" s="8"/>
+      <c r="AI49" s="8"/>
+      <c r="AJ49" s="8"/>
+      <c r="AK49" s="8"/>
+      <c r="AL49" s="8"/>
+      <c r="AM49" s="8"/>
+      <c r="AN49" s="8"/>
+      <c r="AO49" s="8"/>
+      <c r="AP49" s="8"/>
+      <c r="AQ49" s="8"/>
+      <c r="AU49" s="17"/>
+    </row>
+    <row r="50" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B50" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="8"/>
+      <c r="S50" s="8"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="8"/>
+      <c r="V50" s="8"/>
+      <c r="W50" s="8"/>
+      <c r="X50" s="8"/>
+      <c r="Y50" s="8"/>
+      <c r="Z50" s="8"/>
+      <c r="AA50" s="8"/>
+      <c r="AB50" s="8"/>
+      <c r="AC50" s="8"/>
+      <c r="AD50" s="8"/>
+      <c r="AI50" s="8"/>
+      <c r="AJ50" s="8"/>
+      <c r="AK50" s="8"/>
+      <c r="AL50" s="8"/>
+      <c r="AM50" s="8"/>
+      <c r="AN50" s="8"/>
+      <c r="AO50" s="8"/>
+      <c r="AP50" s="8"/>
+      <c r="AQ50" s="8"/>
+      <c r="AU50" s="17"/>
+    </row>
+    <row r="51" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B51" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="8"/>
+      <c r="S51" s="8"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="8"/>
+      <c r="V51" s="8"/>
+      <c r="W51" s="8"/>
+      <c r="X51" s="8"/>
+      <c r="Y51" s="8"/>
+      <c r="Z51" s="8"/>
+      <c r="AA51" s="8"/>
+      <c r="AB51" s="8"/>
+      <c r="AC51" s="8"/>
+      <c r="AD51" s="8"/>
+      <c r="AE51" s="8"/>
+      <c r="AF51" s="8"/>
+      <c r="AG51" s="8"/>
+      <c r="AH51" s="8"/>
+      <c r="AI51" s="8"/>
+      <c r="AJ51" s="8"/>
+      <c r="AK51" s="8"/>
+      <c r="AL51" s="8"/>
+      <c r="AM51" s="8"/>
+      <c r="AN51" s="8"/>
+      <c r="AO51" s="8"/>
+      <c r="AP51" s="8"/>
+      <c r="AQ51" s="8"/>
+      <c r="AR51" s="8"/>
+      <c r="AS51" s="8"/>
+      <c r="AT51" s="8"/>
+      <c r="AU51" s="8"/>
+    </row>
+    <row r="52" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B52" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="8">
+        <v>30</v>
+      </c>
+      <c r="V52" s="8">
+        <v>20</v>
+      </c>
+      <c r="W52" s="8">
+        <v>10</v>
+      </c>
+      <c r="X52" s="8"/>
+      <c r="Y52" s="8">
+        <v>10</v>
+      </c>
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="8"/>
+      <c r="AB52" s="8"/>
+      <c r="AC52" s="8"/>
+      <c r="AD52" s="8"/>
+      <c r="AE52" s="8"/>
+      <c r="AF52" s="8"/>
+      <c r="AG52" s="8"/>
+      <c r="AH52" s="8"/>
+      <c r="AI52" s="8"/>
+      <c r="AJ52" s="8"/>
+      <c r="AK52" s="8"/>
+      <c r="AL52" s="8"/>
+      <c r="AM52" s="8"/>
+      <c r="AN52" s="8"/>
+      <c r="AO52" s="8"/>
+      <c r="AP52" s="8"/>
+      <c r="AQ52" s="8"/>
+      <c r="AU52" s="17"/>
+    </row>
+    <row r="53" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B53" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="16"/>
+      <c r="R53" s="16"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="16"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="16"/>
+      <c r="AI53" s="16"/>
+      <c r="AJ53" s="16"/>
+      <c r="AK53" s="16"/>
+      <c r="AL53" s="16"/>
+      <c r="AM53" s="16"/>
+      <c r="AN53" s="16"/>
+      <c r="AO53" s="16"/>
+      <c r="AP53" s="16"/>
+      <c r="AQ53" s="16"/>
+      <c r="AR53" s="12"/>
+      <c r="AS53" s="12"/>
+      <c r="AT53" s="12"/>
+      <c r="AU53" s="15"/>
+    </row>
+    <row r="54" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B54" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="16"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="8"/>
+      <c r="S54" s="8"/>
+      <c r="T54" s="16"/>
+      <c r="U54" s="8"/>
+      <c r="V54" s="8"/>
+      <c r="W54" s="8"/>
+      <c r="X54" s="8"/>
+      <c r="Y54" s="52">
+        <v>15</v>
+      </c>
+      <c r="Z54" s="52">
+        <v>20</v>
+      </c>
+      <c r="AA54" s="8"/>
+      <c r="AB54" s="16"/>
+      <c r="AC54" s="8"/>
+      <c r="AD54" s="8"/>
+      <c r="AE54" s="8"/>
+      <c r="AF54" s="8"/>
+      <c r="AG54" s="8"/>
+      <c r="AH54" s="8"/>
+      <c r="AI54" s="8"/>
+      <c r="AJ54" s="16"/>
+      <c r="AK54" s="8"/>
+      <c r="AL54" s="8"/>
+      <c r="AM54" s="8"/>
+      <c r="AN54" s="8"/>
+      <c r="AO54" s="8"/>
+      <c r="AP54" s="8"/>
+      <c r="AQ54" s="8"/>
+      <c r="AR54" s="12"/>
+      <c r="AU54" s="17"/>
+    </row>
+    <row r="55" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B55" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="12"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="8"/>
+      <c r="S55" s="8"/>
+      <c r="T55" s="16"/>
+      <c r="U55" s="8"/>
+      <c r="V55" s="8"/>
+      <c r="W55" s="8"/>
+      <c r="X55" s="8"/>
+      <c r="AA55" s="8"/>
+      <c r="AB55" s="16"/>
+      <c r="AC55" s="8"/>
+      <c r="AD55" s="8"/>
+      <c r="AE55" s="8"/>
+      <c r="AF55" s="8"/>
+      <c r="AG55" s="8"/>
+      <c r="AH55" s="8"/>
+      <c r="AI55" s="8"/>
+      <c r="AJ55" s="16"/>
+      <c r="AK55" s="8"/>
+      <c r="AL55" s="8"/>
+      <c r="AM55" s="8"/>
+      <c r="AN55" s="8"/>
+      <c r="AO55" s="8"/>
+      <c r="AP55" s="8"/>
+      <c r="AQ55" s="8"/>
+      <c r="AR55" s="12"/>
+      <c r="AU55" s="17"/>
+    </row>
+    <row r="56" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B56" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D56" s="1">
+        <f t="shared" ref="D56:D57" si="7">COUNTA(M56:AQ56)</f>
+        <v>2</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="8"/>
+      <c r="S56" s="8"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="8"/>
+      <c r="V56" s="8"/>
+      <c r="W56" s="8"/>
+      <c r="X56" s="8"/>
+      <c r="Y56" s="36">
+        <v>10</v>
+      </c>
+      <c r="Z56" s="36">
+        <v>20</v>
+      </c>
+      <c r="AA56" s="8"/>
+      <c r="AB56" s="16"/>
+      <c r="AC56" s="8"/>
+      <c r="AD56" s="8"/>
+      <c r="AE56" s="8"/>
+      <c r="AF56" s="8"/>
+      <c r="AG56" s="8"/>
+      <c r="AH56" s="8"/>
+      <c r="AI56" s="8"/>
+      <c r="AJ56" s="16"/>
+      <c r="AK56" s="8"/>
+      <c r="AL56" s="8"/>
+      <c r="AM56" s="8"/>
+      <c r="AN56" s="8"/>
+      <c r="AO56" s="8"/>
+      <c r="AP56" s="8"/>
+      <c r="AQ56" s="8"/>
+      <c r="AR56" s="12"/>
+      <c r="AU56" s="17"/>
+    </row>
+    <row r="57" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B57" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="1">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F57" s="12"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="8"/>
+      <c r="S57" s="8"/>
+      <c r="T57" s="16"/>
+      <c r="U57" s="8"/>
+      <c r="V57" s="8"/>
+      <c r="W57" s="8"/>
+      <c r="X57" s="8"/>
+      <c r="Y57" s="36">
+        <v>10</v>
+      </c>
+      <c r="Z57" s="36">
+        <v>20</v>
+      </c>
+      <c r="AA57" s="8"/>
+      <c r="AB57" s="16"/>
+      <c r="AC57" s="8"/>
+      <c r="AD57" s="8"/>
+      <c r="AE57" s="8"/>
+      <c r="AF57" s="8"/>
+      <c r="AG57" s="8"/>
+      <c r="AH57" s="8"/>
+      <c r="AI57" s="8"/>
+      <c r="AJ57" s="16"/>
+      <c r="AK57" s="8"/>
+      <c r="AL57" s="8"/>
+      <c r="AM57" s="8"/>
+      <c r="AN57" s="8"/>
+      <c r="AO57" s="8"/>
+      <c r="AP57" s="8"/>
+      <c r="AQ57" s="8"/>
+      <c r="AR57" s="12"/>
+      <c r="AU57" s="17"/>
+    </row>
+    <row r="58" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B58" s="19"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="7"/>
+      <c r="U58" s="6"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
+      <c r="X58" s="6"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="6"/>
+      <c r="AB58" s="7"/>
+      <c r="AC58" s="6"/>
+      <c r="AD58" s="6"/>
+      <c r="AE58" s="6"/>
+      <c r="AF58" s="6"/>
+      <c r="AG58" s="6"/>
+      <c r="AH58" s="6"/>
+      <c r="AI58" s="6"/>
+      <c r="AJ58" s="7"/>
+      <c r="AK58" s="6"/>
+      <c r="AL58" s="6"/>
+      <c r="AM58" s="6"/>
+      <c r="AN58" s="6"/>
+      <c r="AO58" s="6"/>
+      <c r="AP58" s="6"/>
+      <c r="AQ58" s="6"/>
+      <c r="AR58" s="5"/>
+      <c r="AS58" s="2"/>
+      <c r="AT58" s="2"/>
+      <c r="AU58" s="20"/>
+    </row>
+    <row r="59" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B59" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="1">
+        <f>COUNTA(G38:G58)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="42">
+        <f>COUNTA(H38:H58)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="1">
+        <f>COUNTA(I38:I58)</f>
+        <v>1</v>
+      </c>
+      <c r="J59" s="1">
+        <f>COUNTA(J38:J58)</f>
+        <v>1</v>
+      </c>
+      <c r="K59" s="1">
+        <f>COUNTA(K38:K58)</f>
+        <v>1</v>
+      </c>
+      <c r="L59" s="12"/>
+      <c r="M59" s="1">
+        <f t="shared" ref="M59:S59" si="8">COUNTA(M38:M58)</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O59" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="P59" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q59" s="1">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="R59" s="1">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="S59" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="12"/>
+      <c r="U59" s="1">
+        <f t="shared" ref="U59:AA59" si="9">COUNTA(U38:U58)</f>
+        <v>1</v>
+      </c>
+      <c r="V59" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="W59" s="1">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="X59" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="1">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="Z59" s="1">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="AA59" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB59" s="12"/>
+      <c r="AC59" s="1">
+        <f t="shared" ref="AC59:AI59" si="10">COUNTA(AC38:AC58)</f>
+        <v>0</v>
+      </c>
+      <c r="AD59" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AF59" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AG59" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AH59" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AI59" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="12"/>
+      <c r="AK59" s="1">
+        <f t="shared" ref="AK59:AP59" si="11">COUNTA(AK38:AK58)</f>
+        <v>0</v>
+      </c>
+      <c r="AL59" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AM59" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN59" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AO59" s="1">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AP59" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="1">
+        <f t="shared" ref="AQ59" si="12">COUNTA(AQ38:AQ58)</f>
+        <v>0</v>
+      </c>
+      <c r="AR59" s="12"/>
+      <c r="AU59" s="17"/>
+    </row>
+    <row r="60" spans="2:47" x14ac:dyDescent="0.15">
+      <c r="B60" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="5">
+        <f>SUM(G59:AQ59)</f>
+        <v>19</v>
+      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="5"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="2"/>
+      <c r="Z60" s="2"/>
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="5"/>
+      <c r="AC60" s="2"/>
+      <c r="AD60" s="2"/>
+      <c r="AE60" s="2"/>
+      <c r="AF60" s="2"/>
+      <c r="AG60" s="2"/>
+      <c r="AH60" s="2"/>
+      <c r="AI60" s="2"/>
+      <c r="AJ60" s="5"/>
+      <c r="AK60" s="2"/>
+      <c r="AL60" s="2"/>
+      <c r="AM60" s="2"/>
+      <c r="AN60" s="2"/>
+      <c r="AO60" s="2"/>
+      <c r="AP60" s="2"/>
+      <c r="AQ60" s="2"/>
+      <c r="AR60" s="5"/>
+      <c r="AS60" s="2"/>
+      <c r="AT60" s="2"/>
+      <c r="AU60" s="20"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="AU30:AU31" name="Range1"/>
+  </protectedRanges>
+  <mergeCells count="12">
+    <mergeCell ref="M3:S3"/>
+    <mergeCell ref="I2:AQ2"/>
+    <mergeCell ref="AS36:AU36"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AK3:AQ3"/>
+    <mergeCell ref="AC3:AI3"/>
+    <mergeCell ref="U3:AA3"/>
+    <mergeCell ref="I35:AQ35"/>
+    <mergeCell ref="M36:S36"/>
+    <mergeCell ref="U36:AA36"/>
+    <mergeCell ref="AC36:AI36"/>
+    <mergeCell ref="AK36:AQ36"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C6:C25 C26:D38 C39:C57 C58:D60">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14:D25">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39:D57">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions gridLines="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="32" max="16383" man="1"/>
+  </rowBreaks>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="D3:AI12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8215,13 +11711,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDE0023-68AE-6346-90F5-B5E2219C74B5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>